--- a/outputs/Arac_Planlama.xlsx
+++ b/outputs/Arac_Planlama.xlsx
@@ -17,9 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -50,9 +49,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -462,7 +462,7 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -491,7 +491,7 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -520,7 +520,7 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -549,7 +549,7 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -578,7 +578,7 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -607,7 +607,7 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -636,7 +636,7 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -665,7 +665,7 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -694,7 +694,7 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -723,7 +723,7 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -752,7 +752,7 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -781,7 +781,7 @@
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -810,7 +810,7 @@
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -839,7 +839,7 @@
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -868,7 +868,7 @@
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -897,7 +897,7 @@
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -926,7 +926,7 @@
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -955,7 +955,7 @@
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -984,7 +984,7 @@
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C20" t="inlineStr">
@@ -1013,7 +1013,7 @@
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C21" t="inlineStr">
@@ -1042,7 +1042,7 @@
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C22" t="inlineStr">
@@ -1071,7 +1071,7 @@
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -1100,7 +1100,7 @@
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -1129,7 +1129,7 @@
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C25" t="inlineStr">
@@ -1158,7 +1158,7 @@
       <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C26" t="inlineStr">
@@ -1187,7 +1187,7 @@
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -1216,7 +1216,7 @@
       <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C28" t="inlineStr">
@@ -1245,7 +1245,7 @@
       <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C29" t="inlineStr">
@@ -1274,7 +1274,7 @@
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C30" t="inlineStr">
@@ -1303,7 +1303,7 @@
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C31" t="inlineStr">
@@ -1332,7 +1332,7 @@
       <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C32" t="inlineStr">
@@ -1361,7 +1361,7 @@
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C33" t="inlineStr">
@@ -1390,7 +1390,7 @@
       <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C34" t="inlineStr">
@@ -1419,7 +1419,7 @@
       <c r="A35" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C35" t="inlineStr">
@@ -1448,7 +1448,7 @@
       <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C36" t="inlineStr">
@@ -1477,7 +1477,7 @@
       <c r="A37" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C37" t="inlineStr">
@@ -1506,7 +1506,7 @@
       <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C38" t="inlineStr">
@@ -1535,7 +1535,7 @@
       <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C39" t="inlineStr">
@@ -1564,7 +1564,7 @@
       <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C40" t="inlineStr">
@@ -1593,7 +1593,7 @@
       <c r="A41" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C41" t="inlineStr">
@@ -1622,7 +1622,7 @@
       <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C42" t="inlineStr">
@@ -1651,7 +1651,7 @@
       <c r="A43" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C43" t="inlineStr">
@@ -1680,7 +1680,7 @@
       <c r="A44" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C44" t="inlineStr">
@@ -1709,7 +1709,7 @@
       <c r="A45" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C45" t="inlineStr">
@@ -1738,7 +1738,7 @@
       <c r="A46" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C46" t="inlineStr">
@@ -1767,7 +1767,7 @@
       <c r="A47" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C47" t="inlineStr">
@@ -1796,7 +1796,7 @@
       <c r="A48" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C48" t="inlineStr">
@@ -1825,7 +1825,7 @@
       <c r="A49" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C49" t="inlineStr">
@@ -1854,7 +1854,7 @@
       <c r="A50" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C50" t="inlineStr">
@@ -1883,7 +1883,7 @@
       <c r="A51" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C51" t="inlineStr">
@@ -1912,7 +1912,7 @@
       <c r="A52" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C52" t="inlineStr">
@@ -1941,7 +1941,7 @@
       <c r="A53" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C53" t="inlineStr">
@@ -1970,7 +1970,7 @@
       <c r="A54" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C54" t="inlineStr">
@@ -1999,7 +1999,7 @@
       <c r="A55" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C55" t="inlineStr">
@@ -2028,7 +2028,7 @@
       <c r="A56" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C56" t="inlineStr">
@@ -2057,7 +2057,7 @@
       <c r="A57" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C57" t="inlineStr">
@@ -2086,7 +2086,7 @@
       <c r="A58" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C58" t="inlineStr">
@@ -2115,7 +2115,7 @@
       <c r="A59" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C59" t="inlineStr">
@@ -2144,7 +2144,7 @@
       <c r="A60" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C60" t="inlineStr">
@@ -2173,7 +2173,7 @@
       <c r="A61" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C61" t="inlineStr">
@@ -2202,7 +2202,7 @@
       <c r="A62" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C62" t="inlineStr">
@@ -2231,7 +2231,7 @@
       <c r="A63" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C63" t="inlineStr">
@@ -2260,7 +2260,7 @@
       <c r="A64" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C64" t="inlineStr">
@@ -2289,7 +2289,7 @@
       <c r="A65" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C65" t="inlineStr">
@@ -2318,7 +2318,7 @@
       <c r="A66" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C66" t="inlineStr">
@@ -2347,7 +2347,7 @@
       <c r="A67" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C67" t="inlineStr">
@@ -2376,7 +2376,7 @@
       <c r="A68" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C68" t="inlineStr">
@@ -2405,7 +2405,7 @@
       <c r="A69" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C69" t="inlineStr">
@@ -2434,7 +2434,7 @@
       <c r="A70" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C70" t="inlineStr">
@@ -2463,7 +2463,7 @@
       <c r="A71" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C71" t="inlineStr">
@@ -2492,7 +2492,7 @@
       <c r="A72" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C72" t="inlineStr">
@@ -2521,7 +2521,7 @@
       <c r="A73" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C73" t="inlineStr">
@@ -2550,7 +2550,7 @@
       <c r="A74" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C74" t="inlineStr">
@@ -2579,7 +2579,7 @@
       <c r="A75" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="1" t="n">
+      <c r="B75" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C75" t="inlineStr">
@@ -2608,7 +2608,7 @@
       <c r="A76" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="1" t="n">
+      <c r="B76" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C76" t="inlineStr">
@@ -2637,7 +2637,7 @@
       <c r="A77" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="1" t="n">
+      <c r="B77" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C77" t="inlineStr">
@@ -2666,7 +2666,7 @@
       <c r="A78" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="1" t="n">
+      <c r="B78" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C78" t="inlineStr">
@@ -2695,7 +2695,7 @@
       <c r="A79" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="1" t="n">
+      <c r="B79" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C79" t="inlineStr">
@@ -2724,7 +2724,7 @@
       <c r="A80" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="1" t="n">
+      <c r="B80" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C80" t="inlineStr">
@@ -2753,7 +2753,7 @@
       <c r="A81" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="1" t="n">
+      <c r="B81" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C81" t="inlineStr">
@@ -2782,7 +2782,7 @@
       <c r="A82" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="1" t="n">
+      <c r="B82" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C82" t="inlineStr">
@@ -2811,7 +2811,7 @@
       <c r="A83" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="1" t="n">
+      <c r="B83" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C83" t="inlineStr">
@@ -2840,7 +2840,7 @@
       <c r="A84" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="1" t="n">
+      <c r="B84" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C84" t="inlineStr">
@@ -2869,7 +2869,7 @@
       <c r="A85" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="1" t="n">
+      <c r="B85" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C85" t="inlineStr">
@@ -2898,7 +2898,7 @@
       <c r="A86" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="1" t="n">
+      <c r="B86" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C86" t="inlineStr">
@@ -2927,7 +2927,7 @@
       <c r="A87" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="1" t="n">
+      <c r="B87" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C87" t="inlineStr">
@@ -2956,7 +2956,7 @@
       <c r="A88" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="1" t="n">
+      <c r="B88" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C88" t="inlineStr">
@@ -2985,7 +2985,7 @@
       <c r="A89" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="1" t="n">
+      <c r="B89" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C89" t="inlineStr">
@@ -3014,7 +3014,7 @@
       <c r="A90" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="1" t="n">
+      <c r="B90" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C90" t="inlineStr">
@@ -3043,7 +3043,7 @@
       <c r="A91" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="1" t="n">
+      <c r="B91" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C91" t="inlineStr">
@@ -3072,7 +3072,7 @@
       <c r="A92" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="1" t="n">
+      <c r="B92" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C92" t="inlineStr">
@@ -3101,7 +3101,7 @@
       <c r="A93" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="1" t="n">
+      <c r="B93" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C93" t="inlineStr">
@@ -3130,7 +3130,7 @@
       <c r="A94" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="1" t="n">
+      <c r="B94" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C94" t="inlineStr">
@@ -3159,7 +3159,7 @@
       <c r="A95" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="1" t="n">
+      <c r="B95" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C95" t="inlineStr">
@@ -3188,7 +3188,7 @@
       <c r="A96" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="1" t="n">
+      <c r="B96" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C96" t="inlineStr">
@@ -3217,7 +3217,7 @@
       <c r="A97" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="1" t="n">
+      <c r="B97" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C97" t="inlineStr">
@@ -3246,7 +3246,7 @@
       <c r="A98" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="1" t="n">
+      <c r="B98" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C98" t="inlineStr">
@@ -3275,7 +3275,7 @@
       <c r="A99" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="1" t="n">
+      <c r="B99" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C99" t="inlineStr">
@@ -3304,7 +3304,7 @@
       <c r="A100" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="1" t="n">
+      <c r="B100" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C100" t="inlineStr">
@@ -3333,7 +3333,7 @@
       <c r="A101" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="1" t="n">
+      <c r="B101" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C101" t="inlineStr">
@@ -3362,7 +3362,7 @@
       <c r="A102" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="1" t="n">
+      <c r="B102" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C102" t="inlineStr">
@@ -3391,7 +3391,7 @@
       <c r="A103" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="1" t="n">
+      <c r="B103" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C103" t="inlineStr">
@@ -3420,7 +3420,7 @@
       <c r="A104" t="n">
         <v>103</v>
       </c>
-      <c r="B104" s="1" t="n">
+      <c r="B104" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C104" t="inlineStr">
@@ -3449,7 +3449,7 @@
       <c r="A105" t="n">
         <v>104</v>
       </c>
-      <c r="B105" s="1" t="n">
+      <c r="B105" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C105" t="inlineStr">
@@ -3478,7 +3478,7 @@
       <c r="A106" t="n">
         <v>105</v>
       </c>
-      <c r="B106" s="1" t="n">
+      <c r="B106" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C106" t="inlineStr">
@@ -3507,7 +3507,7 @@
       <c r="A107" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="1" t="n">
+      <c r="B107" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C107" t="inlineStr">
@@ -3536,7 +3536,7 @@
       <c r="A108" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="1" t="n">
+      <c r="B108" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C108" t="inlineStr">
@@ -3565,7 +3565,7 @@
       <c r="A109" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="1" t="n">
+      <c r="B109" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C109" t="inlineStr">
@@ -3594,7 +3594,7 @@
       <c r="A110" t="n">
         <v>109</v>
       </c>
-      <c r="B110" s="1" t="n">
+      <c r="B110" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C110" t="inlineStr">
@@ -3623,7 +3623,7 @@
       <c r="A111" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="1" t="n">
+      <c r="B111" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C111" t="inlineStr">
@@ -3652,7 +3652,7 @@
       <c r="A112" t="n">
         <v>111</v>
       </c>
-      <c r="B112" s="1" t="n">
+      <c r="B112" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C112" t="inlineStr">
@@ -3681,7 +3681,7 @@
       <c r="A113" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="1" t="n">
+      <c r="B113" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C113" t="inlineStr">
@@ -3710,7 +3710,7 @@
       <c r="A114" t="n">
         <v>113</v>
       </c>
-      <c r="B114" s="1" t="n">
+      <c r="B114" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C114" t="inlineStr">
@@ -3739,7 +3739,7 @@
       <c r="A115" t="n">
         <v>114</v>
       </c>
-      <c r="B115" s="1" t="n">
+      <c r="B115" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C115" t="inlineStr">
@@ -3768,7 +3768,7 @@
       <c r="A116" t="n">
         <v>115</v>
       </c>
-      <c r="B116" s="1" t="n">
+      <c r="B116" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C116" t="inlineStr">
@@ -3797,7 +3797,7 @@
       <c r="A117" t="n">
         <v>116</v>
       </c>
-      <c r="B117" s="1" t="n">
+      <c r="B117" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C117" t="inlineStr">
@@ -3826,7 +3826,7 @@
       <c r="A118" t="n">
         <v>117</v>
       </c>
-      <c r="B118" s="1" t="n">
+      <c r="B118" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C118" t="inlineStr">
@@ -3855,7 +3855,7 @@
       <c r="A119" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="1" t="n">
+      <c r="B119" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C119" t="inlineStr">
@@ -3884,7 +3884,7 @@
       <c r="A120" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="1" t="n">
+      <c r="B120" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C120" t="inlineStr">
@@ -3913,7 +3913,7 @@
       <c r="A121" t="n">
         <v>120</v>
       </c>
-      <c r="B121" s="1" t="n">
+      <c r="B121" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C121" t="inlineStr">
@@ -3942,7 +3942,7 @@
       <c r="A122" t="n">
         <v>121</v>
       </c>
-      <c r="B122" s="1" t="n">
+      <c r="B122" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C122" t="inlineStr">
@@ -3971,7 +3971,7 @@
       <c r="A123" t="n">
         <v>122</v>
       </c>
-      <c r="B123" s="1" t="n">
+      <c r="B123" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C123" t="inlineStr">
@@ -4000,7 +4000,7 @@
       <c r="A124" t="n">
         <v>123</v>
       </c>
-      <c r="B124" s="1" t="n">
+      <c r="B124" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C124" t="inlineStr">
@@ -4029,7 +4029,7 @@
       <c r="A125" t="n">
         <v>124</v>
       </c>
-      <c r="B125" s="1" t="n">
+      <c r="B125" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C125" t="inlineStr">
@@ -4058,7 +4058,7 @@
       <c r="A126" t="n">
         <v>125</v>
       </c>
-      <c r="B126" s="1" t="n">
+      <c r="B126" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C126" t="inlineStr">
@@ -4087,7 +4087,7 @@
       <c r="A127" t="n">
         <v>126</v>
       </c>
-      <c r="B127" s="1" t="n">
+      <c r="B127" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C127" t="inlineStr">
@@ -4116,7 +4116,7 @@
       <c r="A128" t="n">
         <v>127</v>
       </c>
-      <c r="B128" s="1" t="n">
+      <c r="B128" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C128" t="inlineStr">
@@ -4145,7 +4145,7 @@
       <c r="A129" t="n">
         <v>128</v>
       </c>
-      <c r="B129" s="1" t="n">
+      <c r="B129" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C129" t="inlineStr">
@@ -4174,7 +4174,7 @@
       <c r="A130" t="n">
         <v>129</v>
       </c>
-      <c r="B130" s="1" t="n">
+      <c r="B130" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C130" t="inlineStr">
@@ -4203,7 +4203,7 @@
       <c r="A131" t="n">
         <v>130</v>
       </c>
-      <c r="B131" s="1" t="n">
+      <c r="B131" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C131" t="inlineStr">
@@ -4232,7 +4232,7 @@
       <c r="A132" t="n">
         <v>131</v>
       </c>
-      <c r="B132" s="1" t="n">
+      <c r="B132" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C132" t="inlineStr">
@@ -4261,7 +4261,7 @@
       <c r="A133" t="n">
         <v>132</v>
       </c>
-      <c r="B133" s="1" t="n">
+      <c r="B133" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C133" t="inlineStr">
@@ -4290,7 +4290,7 @@
       <c r="A134" t="n">
         <v>133</v>
       </c>
-      <c r="B134" s="1" t="n">
+      <c r="B134" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C134" t="inlineStr">
@@ -4319,7 +4319,7 @@
       <c r="A135" t="n">
         <v>134</v>
       </c>
-      <c r="B135" s="1" t="n">
+      <c r="B135" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C135" t="inlineStr">
@@ -4348,7 +4348,7 @@
       <c r="A136" t="n">
         <v>135</v>
       </c>
-      <c r="B136" s="1" t="n">
+      <c r="B136" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C136" t="inlineStr">
@@ -4377,7 +4377,7 @@
       <c r="A137" t="n">
         <v>136</v>
       </c>
-      <c r="B137" s="1" t="n">
+      <c r="B137" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C137" t="inlineStr">
@@ -4406,7 +4406,7 @@
       <c r="A138" t="n">
         <v>137</v>
       </c>
-      <c r="B138" s="1" t="n">
+      <c r="B138" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C138" t="inlineStr">
@@ -4435,7 +4435,7 @@
       <c r="A139" t="n">
         <v>138</v>
       </c>
-      <c r="B139" s="1" t="n">
+      <c r="B139" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C139" t="inlineStr">
@@ -4464,7 +4464,7 @@
       <c r="A140" t="n">
         <v>139</v>
       </c>
-      <c r="B140" s="1" t="n">
+      <c r="B140" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C140" t="inlineStr">
@@ -4493,7 +4493,7 @@
       <c r="A141" t="n">
         <v>140</v>
       </c>
-      <c r="B141" s="1" t="n">
+      <c r="B141" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C141" t="inlineStr">
@@ -4522,7 +4522,7 @@
       <c r="A142" t="n">
         <v>141</v>
       </c>
-      <c r="B142" s="1" t="n">
+      <c r="B142" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C142" t="inlineStr">
@@ -4551,7 +4551,7 @@
       <c r="A143" t="n">
         <v>142</v>
       </c>
-      <c r="B143" s="1" t="n">
+      <c r="B143" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C143" t="inlineStr">
@@ -4580,7 +4580,7 @@
       <c r="A144" t="n">
         <v>143</v>
       </c>
-      <c r="B144" s="1" t="n">
+      <c r="B144" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C144" t="inlineStr">
@@ -4609,7 +4609,7 @@
       <c r="A145" t="n">
         <v>144</v>
       </c>
-      <c r="B145" s="1" t="n">
+      <c r="B145" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C145" t="inlineStr">
@@ -4638,7 +4638,7 @@
       <c r="A146" t="n">
         <v>145</v>
       </c>
-      <c r="B146" s="1" t="n">
+      <c r="B146" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C146" t="inlineStr">
@@ -4667,7 +4667,7 @@
       <c r="A147" t="n">
         <v>146</v>
       </c>
-      <c r="B147" s="1" t="n">
+      <c r="B147" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C147" t="inlineStr">
@@ -4696,7 +4696,7 @@
       <c r="A148" t="n">
         <v>147</v>
       </c>
-      <c r="B148" s="1" t="n">
+      <c r="B148" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C148" t="inlineStr">
@@ -4725,7 +4725,7 @@
       <c r="A149" t="n">
         <v>148</v>
       </c>
-      <c r="B149" s="1" t="n">
+      <c r="B149" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C149" t="inlineStr">
@@ -4754,7 +4754,7 @@
       <c r="A150" t="n">
         <v>149</v>
       </c>
-      <c r="B150" s="1" t="n">
+      <c r="B150" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C150" t="inlineStr">
@@ -4783,7 +4783,7 @@
       <c r="A151" t="n">
         <v>150</v>
       </c>
-      <c r="B151" s="1" t="n">
+      <c r="B151" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C151" t="inlineStr">
@@ -4812,7 +4812,7 @@
       <c r="A152" t="n">
         <v>151</v>
       </c>
-      <c r="B152" s="1" t="n">
+      <c r="B152" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C152" t="inlineStr">
@@ -4841,7 +4841,7 @@
       <c r="A153" t="n">
         <v>152</v>
       </c>
-      <c r="B153" s="1" t="n">
+      <c r="B153" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C153" t="inlineStr">
@@ -4870,7 +4870,7 @@
       <c r="A154" t="n">
         <v>153</v>
       </c>
-      <c r="B154" s="1" t="n">
+      <c r="B154" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C154" t="inlineStr">
@@ -4899,7 +4899,7 @@
       <c r="A155" t="n">
         <v>154</v>
       </c>
-      <c r="B155" s="1" t="n">
+      <c r="B155" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C155" t="inlineStr">
@@ -4928,7 +4928,7 @@
       <c r="A156" t="n">
         <v>155</v>
       </c>
-      <c r="B156" s="1" t="n">
+      <c r="B156" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C156" t="inlineStr">
@@ -4957,7 +4957,7 @@
       <c r="A157" t="n">
         <v>156</v>
       </c>
-      <c r="B157" s="1" t="n">
+      <c r="B157" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C157" t="inlineStr">
@@ -4986,7 +4986,7 @@
       <c r="A158" t="n">
         <v>157</v>
       </c>
-      <c r="B158" s="1" t="n">
+      <c r="B158" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C158" t="inlineStr">
@@ -5015,7 +5015,7 @@
       <c r="A159" t="n">
         <v>158</v>
       </c>
-      <c r="B159" s="1" t="n">
+      <c r="B159" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C159" t="inlineStr">
@@ -5044,7 +5044,7 @@
       <c r="A160" t="n">
         <v>159</v>
       </c>
-      <c r="B160" s="1" t="n">
+      <c r="B160" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C160" t="inlineStr">
@@ -5073,7 +5073,7 @@
       <c r="A161" t="n">
         <v>160</v>
       </c>
-      <c r="B161" s="1" t="n">
+      <c r="B161" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C161" t="inlineStr">
@@ -5102,7 +5102,7 @@
       <c r="A162" t="n">
         <v>161</v>
       </c>
-      <c r="B162" s="1" t="n">
+      <c r="B162" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C162" t="inlineStr">
@@ -5131,7 +5131,7 @@
       <c r="A163" t="n">
         <v>162</v>
       </c>
-      <c r="B163" s="1" t="n">
+      <c r="B163" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C163" t="inlineStr">
@@ -5160,7 +5160,7 @@
       <c r="A164" t="n">
         <v>163</v>
       </c>
-      <c r="B164" s="1" t="n">
+      <c r="B164" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C164" t="inlineStr">
@@ -5189,7 +5189,7 @@
       <c r="A165" t="n">
         <v>164</v>
       </c>
-      <c r="B165" s="1" t="n">
+      <c r="B165" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C165" t="inlineStr">
@@ -5218,7 +5218,7 @@
       <c r="A166" t="n">
         <v>165</v>
       </c>
-      <c r="B166" s="1" t="n">
+      <c r="B166" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C166" t="inlineStr">
@@ -5247,7 +5247,7 @@
       <c r="A167" t="n">
         <v>166</v>
       </c>
-      <c r="B167" s="1" t="n">
+      <c r="B167" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C167" t="inlineStr">
@@ -5276,7 +5276,7 @@
       <c r="A168" t="n">
         <v>167</v>
       </c>
-      <c r="B168" s="1" t="n">
+      <c r="B168" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C168" t="inlineStr">
@@ -5305,7 +5305,7 @@
       <c r="A169" t="n">
         <v>168</v>
       </c>
-      <c r="B169" s="1" t="n">
+      <c r="B169" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C169" t="inlineStr">
@@ -5334,7 +5334,7 @@
       <c r="A170" t="n">
         <v>169</v>
       </c>
-      <c r="B170" s="1" t="n">
+      <c r="B170" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C170" t="inlineStr">
@@ -5363,7 +5363,7 @@
       <c r="A171" t="n">
         <v>170</v>
       </c>
-      <c r="B171" s="1" t="n">
+      <c r="B171" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C171" t="inlineStr">
@@ -5392,7 +5392,7 @@
       <c r="A172" t="n">
         <v>171</v>
       </c>
-      <c r="B172" s="1" t="n">
+      <c r="B172" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C172" t="inlineStr">
@@ -5421,7 +5421,7 @@
       <c r="A173" t="n">
         <v>172</v>
       </c>
-      <c r="B173" s="1" t="n">
+      <c r="B173" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C173" t="inlineStr">
@@ -5450,7 +5450,7 @@
       <c r="A174" t="n">
         <v>173</v>
       </c>
-      <c r="B174" s="1" t="n">
+      <c r="B174" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C174" t="inlineStr">
@@ -5479,7 +5479,7 @@
       <c r="A175" t="n">
         <v>174</v>
       </c>
-      <c r="B175" s="1" t="n">
+      <c r="B175" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C175" t="inlineStr">
@@ -5508,7 +5508,7 @@
       <c r="A176" t="n">
         <v>175</v>
       </c>
-      <c r="B176" s="1" t="n">
+      <c r="B176" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C176" t="inlineStr">
@@ -5537,7 +5537,7 @@
       <c r="A177" t="n">
         <v>176</v>
       </c>
-      <c r="B177" s="1" t="n">
+      <c r="B177" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C177" t="inlineStr">
@@ -5566,7 +5566,7 @@
       <c r="A178" t="n">
         <v>177</v>
       </c>
-      <c r="B178" s="1" t="n">
+      <c r="B178" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C178" t="inlineStr">
@@ -5595,7 +5595,7 @@
       <c r="A179" t="n">
         <v>178</v>
       </c>
-      <c r="B179" s="1" t="n">
+      <c r="B179" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C179" t="inlineStr">
@@ -5624,7 +5624,7 @@
       <c r="A180" t="n">
         <v>179</v>
       </c>
-      <c r="B180" s="1" t="n">
+      <c r="B180" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C180" t="inlineStr">
@@ -5653,7 +5653,7 @@
       <c r="A181" t="n">
         <v>180</v>
       </c>
-      <c r="B181" s="1" t="n">
+      <c r="B181" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C181" t="inlineStr">
@@ -5682,7 +5682,7 @@
       <c r="A182" t="n">
         <v>181</v>
       </c>
-      <c r="B182" s="1" t="n">
+      <c r="B182" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C182" t="inlineStr">
@@ -5711,7 +5711,7 @@
       <c r="A183" t="n">
         <v>182</v>
       </c>
-      <c r="B183" s="1" t="n">
+      <c r="B183" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C183" t="inlineStr">
@@ -5740,7 +5740,7 @@
       <c r="A184" t="n">
         <v>183</v>
       </c>
-      <c r="B184" s="1" t="n">
+      <c r="B184" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C184" t="inlineStr">
@@ -5769,7 +5769,7 @@
       <c r="A185" t="n">
         <v>184</v>
       </c>
-      <c r="B185" s="1" t="n">
+      <c r="B185" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C185" t="inlineStr">
@@ -5798,7 +5798,7 @@
       <c r="A186" t="n">
         <v>185</v>
       </c>
-      <c r="B186" s="1" t="n">
+      <c r="B186" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C186" t="inlineStr">
@@ -5827,7 +5827,7 @@
       <c r="A187" t="n">
         <v>186</v>
       </c>
-      <c r="B187" s="1" t="n">
+      <c r="B187" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C187" t="inlineStr">
@@ -5856,7 +5856,7 @@
       <c r="A188" t="n">
         <v>187</v>
       </c>
-      <c r="B188" s="1" t="n">
+      <c r="B188" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C188" t="inlineStr">
@@ -5885,7 +5885,7 @@
       <c r="A189" t="n">
         <v>188</v>
       </c>
-      <c r="B189" s="1" t="n">
+      <c r="B189" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C189" t="inlineStr">
@@ -5914,7 +5914,7 @@
       <c r="A190" t="n">
         <v>189</v>
       </c>
-      <c r="B190" s="1" t="n">
+      <c r="B190" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C190" t="inlineStr">
@@ -5943,7 +5943,7 @@
       <c r="A191" t="n">
         <v>190</v>
       </c>
-      <c r="B191" s="1" t="n">
+      <c r="B191" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C191" t="inlineStr">
@@ -5972,7 +5972,7 @@
       <c r="A192" t="n">
         <v>191</v>
       </c>
-      <c r="B192" s="1" t="n">
+      <c r="B192" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C192" t="inlineStr">
@@ -6001,7 +6001,7 @@
       <c r="A193" t="n">
         <v>192</v>
       </c>
-      <c r="B193" s="1" t="n">
+      <c r="B193" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C193" t="inlineStr">
@@ -6030,7 +6030,7 @@
       <c r="A194" t="n">
         <v>193</v>
       </c>
-      <c r="B194" s="1" t="n">
+      <c r="B194" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C194" t="inlineStr">
@@ -6059,7 +6059,7 @@
       <c r="A195" t="n">
         <v>194</v>
       </c>
-      <c r="B195" s="1" t="n">
+      <c r="B195" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C195" t="inlineStr">
@@ -6088,7 +6088,7 @@
       <c r="A196" t="n">
         <v>195</v>
       </c>
-      <c r="B196" s="1" t="n">
+      <c r="B196" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C196" t="inlineStr">
@@ -6117,7 +6117,7 @@
       <c r="A197" t="n">
         <v>196</v>
       </c>
-      <c r="B197" s="1" t="n">
+      <c r="B197" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C197" t="inlineStr">
@@ -6146,7 +6146,7 @@
       <c r="A198" t="n">
         <v>197</v>
       </c>
-      <c r="B198" s="1" t="n">
+      <c r="B198" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C198" t="inlineStr">
@@ -6175,7 +6175,7 @@
       <c r="A199" t="n">
         <v>198</v>
       </c>
-      <c r="B199" s="1" t="n">
+      <c r="B199" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C199" t="inlineStr">
@@ -6204,7 +6204,7 @@
       <c r="A200" t="n">
         <v>199</v>
       </c>
-      <c r="B200" s="1" t="n">
+      <c r="B200" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C200" t="inlineStr">
@@ -6233,7 +6233,7 @@
       <c r="A201" t="n">
         <v>200</v>
       </c>
-      <c r="B201" s="1" t="n">
+      <c r="B201" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C201" t="inlineStr">
@@ -6262,7 +6262,7 @@
       <c r="A202" t="n">
         <v>201</v>
       </c>
-      <c r="B202" s="1" t="n">
+      <c r="B202" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C202" t="inlineStr">
@@ -6291,7 +6291,7 @@
       <c r="A203" t="n">
         <v>202</v>
       </c>
-      <c r="B203" s="1" t="n">
+      <c r="B203" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C203" t="inlineStr">
@@ -6320,7 +6320,7 @@
       <c r="A204" t="n">
         <v>203</v>
       </c>
-      <c r="B204" s="1" t="n">
+      <c r="B204" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C204" t="inlineStr">
@@ -6349,7 +6349,7 @@
       <c r="A205" t="n">
         <v>204</v>
       </c>
-      <c r="B205" s="1" t="n">
+      <c r="B205" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C205" t="inlineStr">
@@ -6378,7 +6378,7 @@
       <c r="A206" t="n">
         <v>205</v>
       </c>
-      <c r="B206" s="1" t="n">
+      <c r="B206" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C206" t="inlineStr">
@@ -6407,7 +6407,7 @@
       <c r="A207" t="n">
         <v>206</v>
       </c>
-      <c r="B207" s="1" t="n">
+      <c r="B207" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C207" t="inlineStr">
@@ -6436,7 +6436,7 @@
       <c r="A208" t="n">
         <v>207</v>
       </c>
-      <c r="B208" s="1" t="n">
+      <c r="B208" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C208" t="inlineStr">
@@ -6465,7 +6465,7 @@
       <c r="A209" t="n">
         <v>208</v>
       </c>
-      <c r="B209" s="1" t="n">
+      <c r="B209" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C209" t="inlineStr">
@@ -6494,7 +6494,7 @@
       <c r="A210" t="n">
         <v>209</v>
       </c>
-      <c r="B210" s="1" t="n">
+      <c r="B210" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C210" t="inlineStr">
@@ -6523,7 +6523,7 @@
       <c r="A211" t="n">
         <v>210</v>
       </c>
-      <c r="B211" s="1" t="n">
+      <c r="B211" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C211" t="inlineStr">
@@ -6552,7 +6552,7 @@
       <c r="A212" t="n">
         <v>211</v>
       </c>
-      <c r="B212" s="1" t="n">
+      <c r="B212" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C212" t="inlineStr">
@@ -6581,7 +6581,7 @@
       <c r="A213" t="n">
         <v>212</v>
       </c>
-      <c r="B213" s="1" t="n">
+      <c r="B213" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C213" t="inlineStr">
@@ -6610,7 +6610,7 @@
       <c r="A214" t="n">
         <v>213</v>
       </c>
-      <c r="B214" s="1" t="n">
+      <c r="B214" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C214" t="inlineStr">
@@ -6639,7 +6639,7 @@
       <c r="A215" t="n">
         <v>214</v>
       </c>
-      <c r="B215" s="1" t="n">
+      <c r="B215" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C215" t="inlineStr">
@@ -6668,7 +6668,7 @@
       <c r="A216" t="n">
         <v>215</v>
       </c>
-      <c r="B216" s="1" t="n">
+      <c r="B216" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C216" t="inlineStr">
@@ -6697,7 +6697,7 @@
       <c r="A217" t="n">
         <v>216</v>
       </c>
-      <c r="B217" s="1" t="n">
+      <c r="B217" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C217" t="inlineStr">
@@ -6726,7 +6726,7 @@
       <c r="A218" t="n">
         <v>217</v>
       </c>
-      <c r="B218" s="1" t="n">
+      <c r="B218" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C218" t="inlineStr">
@@ -6755,7 +6755,7 @@
       <c r="A219" t="n">
         <v>218</v>
       </c>
-      <c r="B219" s="1" t="n">
+      <c r="B219" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C219" t="inlineStr">
@@ -6784,7 +6784,7 @@
       <c r="A220" t="n">
         <v>219</v>
       </c>
-      <c r="B220" s="1" t="n">
+      <c r="B220" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C220" t="inlineStr">
@@ -6813,7 +6813,7 @@
       <c r="A221" t="n">
         <v>220</v>
       </c>
-      <c r="B221" s="1" t="n">
+      <c r="B221" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C221" t="inlineStr">
@@ -6842,7 +6842,7 @@
       <c r="A222" t="n">
         <v>221</v>
       </c>
-      <c r="B222" s="1" t="n">
+      <c r="B222" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C222" t="inlineStr">
@@ -6871,7 +6871,7 @@
       <c r="A223" t="n">
         <v>222</v>
       </c>
-      <c r="B223" s="1" t="n">
+      <c r="B223" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C223" t="inlineStr">
@@ -6900,7 +6900,7 @@
       <c r="A224" t="n">
         <v>223</v>
       </c>
-      <c r="B224" s="1" t="n">
+      <c r="B224" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C224" t="inlineStr">
@@ -6929,7 +6929,7 @@
       <c r="A225" t="n">
         <v>224</v>
       </c>
-      <c r="B225" s="1" t="n">
+      <c r="B225" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C225" t="inlineStr">
@@ -6958,7 +6958,7 @@
       <c r="A226" t="n">
         <v>225</v>
       </c>
-      <c r="B226" s="1" t="n">
+      <c r="B226" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C226" t="inlineStr">
@@ -6987,7 +6987,7 @@
       <c r="A227" t="n">
         <v>226</v>
       </c>
-      <c r="B227" s="1" t="n">
+      <c r="B227" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C227" t="inlineStr">
@@ -7016,7 +7016,7 @@
       <c r="A228" t="n">
         <v>227</v>
       </c>
-      <c r="B228" s="1" t="n">
+      <c r="B228" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C228" t="inlineStr">
@@ -7045,7 +7045,7 @@
       <c r="A229" t="n">
         <v>228</v>
       </c>
-      <c r="B229" s="1" t="n">
+      <c r="B229" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C229" t="inlineStr">
@@ -7074,7 +7074,7 @@
       <c r="A230" t="n">
         <v>229</v>
       </c>
-      <c r="B230" s="1" t="n">
+      <c r="B230" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C230" t="inlineStr">
@@ -7103,7 +7103,7 @@
       <c r="A231" t="n">
         <v>230</v>
       </c>
-      <c r="B231" s="1" t="n">
+      <c r="B231" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C231" t="inlineStr">
@@ -7132,7 +7132,7 @@
       <c r="A232" t="n">
         <v>231</v>
       </c>
-      <c r="B232" s="1" t="n">
+      <c r="B232" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C232" t="inlineStr">
@@ -7161,7 +7161,7 @@
       <c r="A233" t="n">
         <v>232</v>
       </c>
-      <c r="B233" s="1" t="n">
+      <c r="B233" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C233" t="inlineStr">
@@ -7190,7 +7190,7 @@
       <c r="A234" t="n">
         <v>233</v>
       </c>
-      <c r="B234" s="1" t="n">
+      <c r="B234" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C234" t="inlineStr">
@@ -7219,7 +7219,7 @@
       <c r="A235" t="n">
         <v>234</v>
       </c>
-      <c r="B235" s="1" t="n">
+      <c r="B235" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C235" t="inlineStr">
@@ -7248,7 +7248,7 @@
       <c r="A236" t="n">
         <v>235</v>
       </c>
-      <c r="B236" s="1" t="n">
+      <c r="B236" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C236" t="inlineStr">
@@ -7277,7 +7277,7 @@
       <c r="A237" t="n">
         <v>236</v>
       </c>
-      <c r="B237" s="1" t="n">
+      <c r="B237" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C237" t="inlineStr">
@@ -7306,7 +7306,7 @@
       <c r="A238" t="n">
         <v>237</v>
       </c>
-      <c r="B238" s="1" t="n">
+      <c r="B238" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C238" t="inlineStr">
@@ -7335,7 +7335,7 @@
       <c r="A239" t="n">
         <v>238</v>
       </c>
-      <c r="B239" s="1" t="n">
+      <c r="B239" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C239" t="inlineStr">
@@ -7364,7 +7364,7 @@
       <c r="A240" t="n">
         <v>239</v>
       </c>
-      <c r="B240" s="1" t="n">
+      <c r="B240" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C240" t="inlineStr">
@@ -7393,7 +7393,7 @@
       <c r="A241" t="n">
         <v>240</v>
       </c>
-      <c r="B241" s="1" t="n">
+      <c r="B241" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C241" t="inlineStr">
@@ -7422,7 +7422,7 @@
       <c r="A242" t="n">
         <v>241</v>
       </c>
-      <c r="B242" s="1" t="n">
+      <c r="B242" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C242" t="inlineStr">
@@ -7451,7 +7451,7 @@
       <c r="A243" t="n">
         <v>242</v>
       </c>
-      <c r="B243" s="1" t="n">
+      <c r="B243" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C243" t="inlineStr">
@@ -7480,7 +7480,7 @@
       <c r="A244" t="n">
         <v>243</v>
       </c>
-      <c r="B244" s="1" t="n">
+      <c r="B244" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C244" t="inlineStr">
@@ -7509,7 +7509,7 @@
       <c r="A245" t="n">
         <v>244</v>
       </c>
-      <c r="B245" s="1" t="n">
+      <c r="B245" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C245" t="inlineStr">
@@ -7538,7 +7538,7 @@
       <c r="A246" t="n">
         <v>245</v>
       </c>
-      <c r="B246" s="1" t="n">
+      <c r="B246" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C246" t="inlineStr">
@@ -7567,7 +7567,7 @@
       <c r="A247" t="n">
         <v>246</v>
       </c>
-      <c r="B247" s="1" t="n">
+      <c r="B247" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C247" t="inlineStr">
@@ -7596,7 +7596,7 @@
       <c r="A248" t="n">
         <v>247</v>
       </c>
-      <c r="B248" s="1" t="n">
+      <c r="B248" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C248" t="inlineStr">
@@ -7625,7 +7625,7 @@
       <c r="A249" t="n">
         <v>248</v>
       </c>
-      <c r="B249" s="1" t="n">
+      <c r="B249" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C249" t="inlineStr">
@@ -7654,7 +7654,7 @@
       <c r="A250" t="n">
         <v>249</v>
       </c>
-      <c r="B250" s="1" t="n">
+      <c r="B250" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C250" t="inlineStr">
@@ -7683,7 +7683,7 @@
       <c r="A251" t="n">
         <v>250</v>
       </c>
-      <c r="B251" s="1" t="n">
+      <c r="B251" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C251" t="inlineStr">
@@ -7712,7 +7712,7 @@
       <c r="A252" t="n">
         <v>251</v>
       </c>
-      <c r="B252" s="1" t="n">
+      <c r="B252" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C252" t="inlineStr">
@@ -7741,7 +7741,7 @@
       <c r="A253" t="n">
         <v>252</v>
       </c>
-      <c r="B253" s="1" t="n">
+      <c r="B253" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C253" t="inlineStr">
@@ -7770,7 +7770,7 @@
       <c r="A254" t="n">
         <v>253</v>
       </c>
-      <c r="B254" s="1" t="n">
+      <c r="B254" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C254" t="inlineStr">
@@ -7799,7 +7799,7 @@
       <c r="A255" t="n">
         <v>254</v>
       </c>
-      <c r="B255" s="1" t="n">
+      <c r="B255" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C255" t="inlineStr">
@@ -7828,7 +7828,7 @@
       <c r="A256" t="n">
         <v>255</v>
       </c>
-      <c r="B256" s="1" t="n">
+      <c r="B256" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C256" t="inlineStr">
@@ -7857,7 +7857,7 @@
       <c r="A257" t="n">
         <v>256</v>
       </c>
-      <c r="B257" s="1" t="n">
+      <c r="B257" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C257" t="inlineStr">
@@ -7886,7 +7886,7 @@
       <c r="A258" t="n">
         <v>257</v>
       </c>
-      <c r="B258" s="1" t="n">
+      <c r="B258" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C258" t="inlineStr">
@@ -7915,7 +7915,7 @@
       <c r="A259" t="n">
         <v>258</v>
       </c>
-      <c r="B259" s="1" t="n">
+      <c r="B259" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C259" t="inlineStr">
@@ -7944,7 +7944,7 @@
       <c r="A260" t="n">
         <v>259</v>
       </c>
-      <c r="B260" s="1" t="n">
+      <c r="B260" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C260" t="inlineStr">
@@ -7973,7 +7973,7 @@
       <c r="A261" t="n">
         <v>260</v>
       </c>
-      <c r="B261" s="1" t="n">
+      <c r="B261" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C261" t="inlineStr">
@@ -8002,7 +8002,7 @@
       <c r="A262" t="n">
         <v>261</v>
       </c>
-      <c r="B262" s="1" t="n">
+      <c r="B262" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C262" t="inlineStr">
@@ -8031,7 +8031,7 @@
       <c r="A263" t="n">
         <v>262</v>
       </c>
-      <c r="B263" s="1" t="n">
+      <c r="B263" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C263" t="inlineStr">
@@ -8060,7 +8060,7 @@
       <c r="A264" t="n">
         <v>263</v>
       </c>
-      <c r="B264" s="1" t="n">
+      <c r="B264" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C264" t="inlineStr">
@@ -8089,7 +8089,7 @@
       <c r="A265" t="n">
         <v>264</v>
       </c>
-      <c r="B265" s="1" t="n">
+      <c r="B265" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C265" t="inlineStr">
@@ -8118,7 +8118,7 @@
       <c r="A266" t="n">
         <v>265</v>
       </c>
-      <c r="B266" s="1" t="n">
+      <c r="B266" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C266" t="inlineStr">
@@ -8147,7 +8147,7 @@
       <c r="A267" t="n">
         <v>266</v>
       </c>
-      <c r="B267" s="1" t="n">
+      <c r="B267" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C267" t="inlineStr">
@@ -8176,7 +8176,7 @@
       <c r="A268" t="n">
         <v>267</v>
       </c>
-      <c r="B268" s="1" t="n">
+      <c r="B268" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C268" t="inlineStr">
@@ -8205,7 +8205,7 @@
       <c r="A269" t="n">
         <v>268</v>
       </c>
-      <c r="B269" s="1" t="n">
+      <c r="B269" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C269" t="inlineStr">
@@ -8234,7 +8234,7 @@
       <c r="A270" t="n">
         <v>269</v>
       </c>
-      <c r="B270" s="1" t="n">
+      <c r="B270" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C270" t="inlineStr">
@@ -8263,7 +8263,7 @@
       <c r="A271" t="n">
         <v>270</v>
       </c>
-      <c r="B271" s="1" t="n">
+      <c r="B271" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C271" t="inlineStr">
@@ -8292,7 +8292,7 @@
       <c r="A272" t="n">
         <v>271</v>
       </c>
-      <c r="B272" s="1" t="n">
+      <c r="B272" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C272" t="inlineStr">
@@ -8321,7 +8321,7 @@
       <c r="A273" t="n">
         <v>272</v>
       </c>
-      <c r="B273" s="1" t="n">
+      <c r="B273" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C273" t="inlineStr">
@@ -8350,7 +8350,7 @@
       <c r="A274" t="n">
         <v>273</v>
       </c>
-      <c r="B274" s="1" t="n">
+      <c r="B274" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C274" t="inlineStr">
@@ -8379,7 +8379,7 @@
       <c r="A275" t="n">
         <v>274</v>
       </c>
-      <c r="B275" s="1" t="n">
+      <c r="B275" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C275" t="inlineStr">
@@ -8408,7 +8408,7 @@
       <c r="A276" t="n">
         <v>275</v>
       </c>
-      <c r="B276" s="1" t="n">
+      <c r="B276" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C276" t="inlineStr">
@@ -8437,7 +8437,7 @@
       <c r="A277" t="n">
         <v>276</v>
       </c>
-      <c r="B277" s="1" t="n">
+      <c r="B277" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C277" t="inlineStr">
@@ -8466,7 +8466,7 @@
       <c r="A278" t="n">
         <v>277</v>
       </c>
-      <c r="B278" s="1" t="n">
+      <c r="B278" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C278" t="inlineStr">
@@ -8495,7 +8495,7 @@
       <c r="A279" t="n">
         <v>278</v>
       </c>
-      <c r="B279" s="1" t="n">
+      <c r="B279" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C279" t="inlineStr">
@@ -8524,7 +8524,7 @@
       <c r="A280" t="n">
         <v>279</v>
       </c>
-      <c r="B280" s="1" t="n">
+      <c r="B280" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C280" t="inlineStr">
@@ -8553,7 +8553,7 @@
       <c r="A281" t="n">
         <v>280</v>
       </c>
-      <c r="B281" s="1" t="n">
+      <c r="B281" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C281" t="inlineStr">
@@ -8582,7 +8582,7 @@
       <c r="A282" t="n">
         <v>281</v>
       </c>
-      <c r="B282" s="1" t="n">
+      <c r="B282" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C282" t="inlineStr">
@@ -8611,7 +8611,7 @@
       <c r="A283" t="n">
         <v>282</v>
       </c>
-      <c r="B283" s="1" t="n">
+      <c r="B283" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C283" t="inlineStr">
@@ -8640,7 +8640,7 @@
       <c r="A284" t="n">
         <v>283</v>
       </c>
-      <c r="B284" s="1" t="n">
+      <c r="B284" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C284" t="inlineStr">
@@ -8669,7 +8669,7 @@
       <c r="A285" t="n">
         <v>284</v>
       </c>
-      <c r="B285" s="1" t="n">
+      <c r="B285" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C285" t="inlineStr">
@@ -8698,7 +8698,7 @@
       <c r="A286" t="n">
         <v>285</v>
       </c>
-      <c r="B286" s="1" t="n">
+      <c r="B286" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C286" t="inlineStr">
@@ -8727,7 +8727,7 @@
       <c r="A287" t="n">
         <v>286</v>
       </c>
-      <c r="B287" s="1" t="n">
+      <c r="B287" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C287" t="inlineStr">
@@ -8756,7 +8756,7 @@
       <c r="A288" t="n">
         <v>287</v>
       </c>
-      <c r="B288" s="1" t="n">
+      <c r="B288" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C288" t="inlineStr">
@@ -8785,7 +8785,7 @@
       <c r="A289" t="n">
         <v>288</v>
       </c>
-      <c r="B289" s="1" t="n">
+      <c r="B289" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C289" t="inlineStr">
@@ -8814,7 +8814,7 @@
       <c r="A290" t="n">
         <v>289</v>
       </c>
-      <c r="B290" s="1" t="n">
+      <c r="B290" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C290" t="inlineStr">
@@ -8843,7 +8843,7 @@
       <c r="A291" t="n">
         <v>290</v>
       </c>
-      <c r="B291" s="1" t="n">
+      <c r="B291" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C291" t="inlineStr">
@@ -8872,7 +8872,7 @@
       <c r="A292" t="n">
         <v>291</v>
       </c>
-      <c r="B292" s="1" t="n">
+      <c r="B292" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C292" t="inlineStr">
@@ -8901,7 +8901,7 @@
       <c r="A293" t="n">
         <v>292</v>
       </c>
-      <c r="B293" s="1" t="n">
+      <c r="B293" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C293" t="inlineStr">
@@ -8930,7 +8930,7 @@
       <c r="A294" t="n">
         <v>293</v>
       </c>
-      <c r="B294" s="1" t="n">
+      <c r="B294" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C294" t="inlineStr">
@@ -8959,7 +8959,7 @@
       <c r="A295" t="n">
         <v>294</v>
       </c>
-      <c r="B295" s="1" t="n">
+      <c r="B295" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C295" t="inlineStr">
@@ -8988,7 +8988,7 @@
       <c r="A296" t="n">
         <v>295</v>
       </c>
-      <c r="B296" s="1" t="n">
+      <c r="B296" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C296" t="inlineStr">
@@ -9017,7 +9017,7 @@
       <c r="A297" t="n">
         <v>296</v>
       </c>
-      <c r="B297" s="1" t="n">
+      <c r="B297" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C297" t="inlineStr">
@@ -9046,7 +9046,7 @@
       <c r="A298" t="n">
         <v>297</v>
       </c>
-      <c r="B298" s="1" t="n">
+      <c r="B298" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C298" t="inlineStr">
@@ -9075,7 +9075,7 @@
       <c r="A299" t="n">
         <v>298</v>
       </c>
-      <c r="B299" s="1" t="n">
+      <c r="B299" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C299" t="inlineStr">
@@ -9104,7 +9104,7 @@
       <c r="A300" t="n">
         <v>299</v>
       </c>
-      <c r="B300" s="1" t="n">
+      <c r="B300" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C300" t="inlineStr">
@@ -9133,7 +9133,7 @@
       <c r="A301" t="n">
         <v>300</v>
       </c>
-      <c r="B301" s="1" t="n">
+      <c r="B301" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C301" t="inlineStr">
@@ -9162,7 +9162,7 @@
       <c r="A302" t="n">
         <v>301</v>
       </c>
-      <c r="B302" s="1" t="n">
+      <c r="B302" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C302" t="inlineStr">
@@ -9191,7 +9191,7 @@
       <c r="A303" t="n">
         <v>302</v>
       </c>
-      <c r="B303" s="1" t="n">
+      <c r="B303" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C303" t="inlineStr">
@@ -9220,7 +9220,7 @@
       <c r="A304" t="n">
         <v>303</v>
       </c>
-      <c r="B304" s="1" t="n">
+      <c r="B304" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C304" t="inlineStr">
@@ -9249,7 +9249,7 @@
       <c r="A305" t="n">
         <v>304</v>
       </c>
-      <c r="B305" s="1" t="n">
+      <c r="B305" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C305" t="inlineStr">
@@ -9278,7 +9278,7 @@
       <c r="A306" t="n">
         <v>305</v>
       </c>
-      <c r="B306" s="1" t="n">
+      <c r="B306" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C306" t="inlineStr">
@@ -9307,7 +9307,7 @@
       <c r="A307" t="n">
         <v>306</v>
       </c>
-      <c r="B307" s="1" t="n">
+      <c r="B307" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C307" t="inlineStr">
@@ -9336,7 +9336,7 @@
       <c r="A308" t="n">
         <v>307</v>
       </c>
-      <c r="B308" s="1" t="n">
+      <c r="B308" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C308" t="inlineStr">
@@ -9365,7 +9365,7 @@
       <c r="A309" t="n">
         <v>308</v>
       </c>
-      <c r="B309" s="1" t="n">
+      <c r="B309" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C309" t="inlineStr">
@@ -9394,7 +9394,7 @@
       <c r="A310" t="n">
         <v>309</v>
       </c>
-      <c r="B310" s="1" t="n">
+      <c r="B310" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C310" t="inlineStr">
@@ -9423,7 +9423,7 @@
       <c r="A311" t="n">
         <v>310</v>
       </c>
-      <c r="B311" s="1" t="n">
+      <c r="B311" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C311" t="inlineStr">
@@ -9452,7 +9452,7 @@
       <c r="A312" t="n">
         <v>311</v>
       </c>
-      <c r="B312" s="1" t="n">
+      <c r="B312" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C312" t="inlineStr">
@@ -9481,7 +9481,7 @@
       <c r="A313" t="n">
         <v>312</v>
       </c>
-      <c r="B313" s="1" t="n">
+      <c r="B313" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C313" t="inlineStr">
@@ -9510,7 +9510,7 @@
       <c r="A314" t="n">
         <v>313</v>
       </c>
-      <c r="B314" s="1" t="n">
+      <c r="B314" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C314" t="inlineStr">
@@ -9539,7 +9539,7 @@
       <c r="A315" t="n">
         <v>314</v>
       </c>
-      <c r="B315" s="1" t="n">
+      <c r="B315" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C315" t="inlineStr">
@@ -9568,7 +9568,7 @@
       <c r="A316" t="n">
         <v>315</v>
       </c>
-      <c r="B316" s="1" t="n">
+      <c r="B316" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C316" t="inlineStr">
@@ -9597,7 +9597,7 @@
       <c r="A317" t="n">
         <v>316</v>
       </c>
-      <c r="B317" s="1" t="n">
+      <c r="B317" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C317" t="inlineStr">
@@ -9626,7 +9626,7 @@
       <c r="A318" t="n">
         <v>317</v>
       </c>
-      <c r="B318" s="1" t="n">
+      <c r="B318" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C318" t="inlineStr">
@@ -9655,7 +9655,7 @@
       <c r="A319" t="n">
         <v>318</v>
       </c>
-      <c r="B319" s="1" t="n">
+      <c r="B319" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C319" t="inlineStr">
@@ -9684,7 +9684,7 @@
       <c r="A320" t="n">
         <v>319</v>
       </c>
-      <c r="B320" s="1" t="n">
+      <c r="B320" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C320" t="inlineStr">
@@ -9713,7 +9713,7 @@
       <c r="A321" t="n">
         <v>320</v>
       </c>
-      <c r="B321" s="1" t="n">
+      <c r="B321" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C321" t="inlineStr">
@@ -9742,7 +9742,7 @@
       <c r="A322" t="n">
         <v>321</v>
       </c>
-      <c r="B322" s="1" t="n">
+      <c r="B322" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C322" t="inlineStr">
@@ -9771,7 +9771,7 @@
       <c r="A323" t="n">
         <v>322</v>
       </c>
-      <c r="B323" s="1" t="n">
+      <c r="B323" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C323" t="inlineStr">
@@ -9800,7 +9800,7 @@
       <c r="A324" t="n">
         <v>323</v>
       </c>
-      <c r="B324" s="1" t="n">
+      <c r="B324" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C324" t="inlineStr">
@@ -9829,7 +9829,7 @@
       <c r="A325" t="n">
         <v>324</v>
       </c>
-      <c r="B325" s="1" t="n">
+      <c r="B325" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C325" t="inlineStr">
@@ -9858,7 +9858,7 @@
       <c r="A326" t="n">
         <v>325</v>
       </c>
-      <c r="B326" s="1" t="n">
+      <c r="B326" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C326" t="inlineStr">
@@ -9887,7 +9887,7 @@
       <c r="A327" t="n">
         <v>326</v>
       </c>
-      <c r="B327" s="1" t="n">
+      <c r="B327" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C327" t="inlineStr">
@@ -9916,7 +9916,7 @@
       <c r="A328" t="n">
         <v>327</v>
       </c>
-      <c r="B328" s="1" t="n">
+      <c r="B328" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C328" t="inlineStr">
@@ -9945,7 +9945,7 @@
       <c r="A329" t="n">
         <v>328</v>
       </c>
-      <c r="B329" s="1" t="n">
+      <c r="B329" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C329" t="inlineStr">
@@ -9974,7 +9974,7 @@
       <c r="A330" t="n">
         <v>329</v>
       </c>
-      <c r="B330" s="1" t="n">
+      <c r="B330" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C330" t="inlineStr">
@@ -10003,7 +10003,7 @@
       <c r="A331" t="n">
         <v>330</v>
       </c>
-      <c r="B331" s="1" t="n">
+      <c r="B331" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C331" t="inlineStr">
@@ -10032,7 +10032,7 @@
       <c r="A332" t="n">
         <v>331</v>
       </c>
-      <c r="B332" s="1" t="n">
+      <c r="B332" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C332" t="inlineStr">
@@ -10061,7 +10061,7 @@
       <c r="A333" t="n">
         <v>332</v>
       </c>
-      <c r="B333" s="1" t="n">
+      <c r="B333" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C333" t="inlineStr">
@@ -10090,7 +10090,7 @@
       <c r="A334" t="n">
         <v>333</v>
       </c>
-      <c r="B334" s="1" t="n">
+      <c r="B334" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C334" t="inlineStr">
@@ -10119,7 +10119,7 @@
       <c r="A335" t="n">
         <v>334</v>
       </c>
-      <c r="B335" s="1" t="n">
+      <c r="B335" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C335" t="inlineStr">
@@ -10148,7 +10148,7 @@
       <c r="A336" t="n">
         <v>335</v>
       </c>
-      <c r="B336" s="1" t="n">
+      <c r="B336" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C336" t="inlineStr">
@@ -10177,7 +10177,7 @@
       <c r="A337" t="n">
         <v>336</v>
       </c>
-      <c r="B337" s="1" t="n">
+      <c r="B337" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C337" t="inlineStr">
@@ -10206,7 +10206,7 @@
       <c r="A338" t="n">
         <v>337</v>
       </c>
-      <c r="B338" s="1" t="n">
+      <c r="B338" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C338" t="inlineStr">
@@ -10235,7 +10235,7 @@
       <c r="A339" t="n">
         <v>338</v>
       </c>
-      <c r="B339" s="1" t="n">
+      <c r="B339" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C339" t="inlineStr">
@@ -10264,7 +10264,7 @@
       <c r="A340" t="n">
         <v>339</v>
       </c>
-      <c r="B340" s="1" t="n">
+      <c r="B340" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C340" t="inlineStr">
@@ -10293,7 +10293,7 @@
       <c r="A341" t="n">
         <v>340</v>
       </c>
-      <c r="B341" s="1" t="n">
+      <c r="B341" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C341" t="inlineStr">
@@ -10322,7 +10322,7 @@
       <c r="A342" t="n">
         <v>341</v>
       </c>
-      <c r="B342" s="1" t="n">
+      <c r="B342" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C342" t="inlineStr">
@@ -10351,7 +10351,7 @@
       <c r="A343" t="n">
         <v>342</v>
       </c>
-      <c r="B343" s="1" t="n">
+      <c r="B343" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C343" t="inlineStr">
@@ -10380,7 +10380,7 @@
       <c r="A344" t="n">
         <v>343</v>
       </c>
-      <c r="B344" s="1" t="n">
+      <c r="B344" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C344" t="inlineStr">
@@ -10409,7 +10409,7 @@
       <c r="A345" t="n">
         <v>344</v>
       </c>
-      <c r="B345" s="1" t="n">
+      <c r="B345" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C345" t="inlineStr">
@@ -10438,7 +10438,7 @@
       <c r="A346" t="n">
         <v>345</v>
       </c>
-      <c r="B346" s="1" t="n">
+      <c r="B346" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C346" t="inlineStr">
@@ -10467,7 +10467,7 @@
       <c r="A347" t="n">
         <v>346</v>
       </c>
-      <c r="B347" s="1" t="n">
+      <c r="B347" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C347" t="inlineStr">
@@ -10496,7 +10496,7 @@
       <c r="A348" t="n">
         <v>347</v>
       </c>
-      <c r="B348" s="1" t="n">
+      <c r="B348" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C348" t="inlineStr">
@@ -10525,7 +10525,7 @@
       <c r="A349" t="n">
         <v>348</v>
       </c>
-      <c r="B349" s="1" t="n">
+      <c r="B349" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C349" t="inlineStr">
@@ -10554,7 +10554,7 @@
       <c r="A350" t="n">
         <v>349</v>
       </c>
-      <c r="B350" s="1" t="n">
+      <c r="B350" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C350" t="inlineStr">
@@ -10583,7 +10583,7 @@
       <c r="A351" t="n">
         <v>350</v>
       </c>
-      <c r="B351" s="1" t="n">
+      <c r="B351" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C351" t="inlineStr">
@@ -10612,7 +10612,7 @@
       <c r="A352" t="n">
         <v>351</v>
       </c>
-      <c r="B352" s="1" t="n">
+      <c r="B352" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C352" t="inlineStr">
@@ -10641,7 +10641,7 @@
       <c r="A353" t="n">
         <v>352</v>
       </c>
-      <c r="B353" s="1" t="n">
+      <c r="B353" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C353" t="inlineStr">
@@ -10670,7 +10670,7 @@
       <c r="A354" t="n">
         <v>353</v>
       </c>
-      <c r="B354" s="1" t="n">
+      <c r="B354" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C354" t="inlineStr">
@@ -10699,7 +10699,7 @@
       <c r="A355" t="n">
         <v>354</v>
       </c>
-      <c r="B355" s="1" t="n">
+      <c r="B355" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C355" t="inlineStr">
@@ -10728,7 +10728,7 @@
       <c r="A356" t="n">
         <v>355</v>
       </c>
-      <c r="B356" s="1" t="n">
+      <c r="B356" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C356" t="inlineStr">
@@ -10757,7 +10757,7 @@
       <c r="A357" t="n">
         <v>356</v>
       </c>
-      <c r="B357" s="1" t="n">
+      <c r="B357" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C357" t="inlineStr">
@@ -10786,7 +10786,7 @@
       <c r="A358" t="n">
         <v>357</v>
       </c>
-      <c r="B358" s="1" t="n">
+      <c r="B358" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C358" t="inlineStr">
@@ -10815,7 +10815,7 @@
       <c r="A359" t="n">
         <v>358</v>
       </c>
-      <c r="B359" s="1" t="n">
+      <c r="B359" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C359" t="inlineStr">
@@ -10844,7 +10844,7 @@
       <c r="A360" t="n">
         <v>359</v>
       </c>
-      <c r="B360" s="1" t="n">
+      <c r="B360" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C360" t="inlineStr">
@@ -10873,7 +10873,7 @@
       <c r="A361" t="n">
         <v>360</v>
       </c>
-      <c r="B361" s="1" t="n">
+      <c r="B361" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C361" t="inlineStr">
@@ -10902,7 +10902,7 @@
       <c r="A362" t="n">
         <v>361</v>
       </c>
-      <c r="B362" s="1" t="n">
+      <c r="B362" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C362" t="inlineStr">
@@ -10931,7 +10931,7 @@
       <c r="A363" t="n">
         <v>362</v>
       </c>
-      <c r="B363" s="1" t="n">
+      <c r="B363" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C363" t="inlineStr">
@@ -10960,7 +10960,7 @@
       <c r="A364" t="n">
         <v>363</v>
       </c>
-      <c r="B364" s="1" t="n">
+      <c r="B364" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C364" t="inlineStr">
@@ -10989,7 +10989,7 @@
       <c r="A365" t="n">
         <v>364</v>
       </c>
-      <c r="B365" s="1" t="n">
+      <c r="B365" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C365" t="inlineStr">
@@ -11018,7 +11018,7 @@
       <c r="A366" t="n">
         <v>365</v>
       </c>
-      <c r="B366" s="1" t="n">
+      <c r="B366" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C366" t="inlineStr">
@@ -11047,7 +11047,7 @@
       <c r="A367" t="n">
         <v>366</v>
       </c>
-      <c r="B367" s="1" t="n">
+      <c r="B367" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C367" t="inlineStr">
@@ -11076,7 +11076,7 @@
       <c r="A368" t="n">
         <v>367</v>
       </c>
-      <c r="B368" s="1" t="n">
+      <c r="B368" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C368" t="inlineStr">
@@ -11105,7 +11105,7 @@
       <c r="A369" t="n">
         <v>368</v>
       </c>
-      <c r="B369" s="1" t="n">
+      <c r="B369" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C369" t="inlineStr">
@@ -11134,7 +11134,7 @@
       <c r="A370" t="n">
         <v>369</v>
       </c>
-      <c r="B370" s="1" t="n">
+      <c r="B370" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C370" t="inlineStr">
@@ -11163,7 +11163,7 @@
       <c r="A371" t="n">
         <v>370</v>
       </c>
-      <c r="B371" s="1" t="n">
+      <c r="B371" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C371" t="inlineStr">
@@ -11192,7 +11192,7 @@
       <c r="A372" t="n">
         <v>371</v>
       </c>
-      <c r="B372" s="1" t="n">
+      <c r="B372" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C372" t="inlineStr">
@@ -11221,7 +11221,7 @@
       <c r="A373" t="n">
         <v>372</v>
       </c>
-      <c r="B373" s="1" t="n">
+      <c r="B373" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C373" t="inlineStr">
@@ -11250,7 +11250,7 @@
       <c r="A374" t="n">
         <v>373</v>
       </c>
-      <c r="B374" s="1" t="n">
+      <c r="B374" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C374" t="inlineStr">
@@ -11279,7 +11279,7 @@
       <c r="A375" t="n">
         <v>374</v>
       </c>
-      <c r="B375" s="1" t="n">
+      <c r="B375" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C375" t="inlineStr">
@@ -11308,7 +11308,7 @@
       <c r="A376" t="n">
         <v>375</v>
       </c>
-      <c r="B376" s="1" t="n">
+      <c r="B376" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C376" t="inlineStr">
@@ -11337,7 +11337,7 @@
       <c r="A377" t="n">
         <v>376</v>
       </c>
-      <c r="B377" s="1" t="n">
+      <c r="B377" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C377" t="inlineStr">
@@ -11366,7 +11366,7 @@
       <c r="A378" t="n">
         <v>377</v>
       </c>
-      <c r="B378" s="1" t="n">
+      <c r="B378" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C378" t="inlineStr">
@@ -11395,7 +11395,7 @@
       <c r="A379" t="n">
         <v>378</v>
       </c>
-      <c r="B379" s="1" t="n">
+      <c r="B379" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C379" t="inlineStr">
@@ -11424,7 +11424,7 @@
       <c r="A380" t="n">
         <v>379</v>
       </c>
-      <c r="B380" s="1" t="n">
+      <c r="B380" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C380" t="inlineStr">
@@ -11453,7 +11453,7 @@
       <c r="A381" t="n">
         <v>380</v>
       </c>
-      <c r="B381" s="1" t="n">
+      <c r="B381" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C381" t="inlineStr">
@@ -11482,7 +11482,7 @@
       <c r="A382" t="n">
         <v>381</v>
       </c>
-      <c r="B382" s="1" t="n">
+      <c r="B382" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C382" t="inlineStr">
@@ -11511,7 +11511,7 @@
       <c r="A383" t="n">
         <v>382</v>
       </c>
-      <c r="B383" s="1" t="n">
+      <c r="B383" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C383" t="inlineStr">
@@ -11540,7 +11540,7 @@
       <c r="A384" t="n">
         <v>383</v>
       </c>
-      <c r="B384" s="1" t="n">
+      <c r="B384" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C384" t="inlineStr">
@@ -11569,7 +11569,7 @@
       <c r="A385" t="n">
         <v>384</v>
       </c>
-      <c r="B385" s="1" t="n">
+      <c r="B385" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C385" t="inlineStr">
@@ -11598,7 +11598,7 @@
       <c r="A386" t="n">
         <v>385</v>
       </c>
-      <c r="B386" s="1" t="n">
+      <c r="B386" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C386" t="inlineStr">
@@ -11627,7 +11627,7 @@
       <c r="A387" t="n">
         <v>386</v>
       </c>
-      <c r="B387" s="1" t="n">
+      <c r="B387" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C387" t="inlineStr">
@@ -11656,7 +11656,7 @@
       <c r="A388" t="n">
         <v>387</v>
       </c>
-      <c r="B388" s="1" t="n">
+      <c r="B388" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C388" t="inlineStr">
@@ -11685,7 +11685,7 @@
       <c r="A389" t="n">
         <v>388</v>
       </c>
-      <c r="B389" s="1" t="n">
+      <c r="B389" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C389" t="inlineStr">
@@ -11714,7 +11714,7 @@
       <c r="A390" t="n">
         <v>389</v>
       </c>
-      <c r="B390" s="1" t="n">
+      <c r="B390" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C390" t="inlineStr">
@@ -11743,7 +11743,7 @@
       <c r="A391" t="n">
         <v>390</v>
       </c>
-      <c r="B391" s="1" t="n">
+      <c r="B391" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C391" t="inlineStr">
@@ -11772,7 +11772,7 @@
       <c r="A392" t="n">
         <v>391</v>
       </c>
-      <c r="B392" s="1" t="n">
+      <c r="B392" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C392" t="inlineStr">
@@ -11801,7 +11801,7 @@
       <c r="A393" t="n">
         <v>392</v>
       </c>
-      <c r="B393" s="1" t="n">
+      <c r="B393" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C393" t="inlineStr">
@@ -11830,7 +11830,7 @@
       <c r="A394" t="n">
         <v>393</v>
       </c>
-      <c r="B394" s="1" t="n">
+      <c r="B394" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C394" t="inlineStr">
@@ -11859,7 +11859,7 @@
       <c r="A395" t="n">
         <v>394</v>
       </c>
-      <c r="B395" s="1" t="n">
+      <c r="B395" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C395" t="inlineStr">
@@ -11888,7 +11888,7 @@
       <c r="A396" t="n">
         <v>395</v>
       </c>
-      <c r="B396" s="1" t="n">
+      <c r="B396" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C396" t="inlineStr">
@@ -11917,7 +11917,7 @@
       <c r="A397" t="n">
         <v>396</v>
       </c>
-      <c r="B397" s="1" t="n">
+      <c r="B397" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C397" t="inlineStr">
@@ -11946,7 +11946,7 @@
       <c r="A398" t="n">
         <v>397</v>
       </c>
-      <c r="B398" s="1" t="n">
+      <c r="B398" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C398" t="inlineStr">
@@ -11975,7 +11975,7 @@
       <c r="A399" t="n">
         <v>398</v>
       </c>
-      <c r="B399" s="1" t="n">
+      <c r="B399" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C399" t="inlineStr">
@@ -12004,7 +12004,7 @@
       <c r="A400" t="n">
         <v>399</v>
       </c>
-      <c r="B400" s="1" t="n">
+      <c r="B400" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C400" t="inlineStr">
@@ -12033,7 +12033,7 @@
       <c r="A401" t="n">
         <v>400</v>
       </c>
-      <c r="B401" s="1" t="n">
+      <c r="B401" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C401" t="inlineStr">
@@ -12062,7 +12062,7 @@
       <c r="A402" t="n">
         <v>401</v>
       </c>
-      <c r="B402" s="1" t="n">
+      <c r="B402" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C402" t="inlineStr">
@@ -12091,7 +12091,7 @@
       <c r="A403" t="n">
         <v>402</v>
       </c>
-      <c r="B403" s="1" t="n">
+      <c r="B403" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C403" t="inlineStr">
@@ -12120,7 +12120,7 @@
       <c r="A404" t="n">
         <v>403</v>
       </c>
-      <c r="B404" s="1" t="n">
+      <c r="B404" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C404" t="inlineStr">
@@ -12149,7 +12149,7 @@
       <c r="A405" t="n">
         <v>404</v>
       </c>
-      <c r="B405" s="1" t="n">
+      <c r="B405" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C405" t="inlineStr">
@@ -12178,7 +12178,7 @@
       <c r="A406" t="n">
         <v>405</v>
       </c>
-      <c r="B406" s="1" t="n">
+      <c r="B406" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C406" t="inlineStr">
@@ -12207,7 +12207,7 @@
       <c r="A407" t="n">
         <v>406</v>
       </c>
-      <c r="B407" s="1" t="n">
+      <c r="B407" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C407" t="inlineStr">
@@ -12236,7 +12236,7 @@
       <c r="A408" t="n">
         <v>407</v>
       </c>
-      <c r="B408" s="1" t="n">
+      <c r="B408" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C408" t="inlineStr">
@@ -12265,7 +12265,7 @@
       <c r="A409" t="n">
         <v>408</v>
       </c>
-      <c r="B409" s="1" t="n">
+      <c r="B409" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C409" t="inlineStr">
@@ -12294,7 +12294,7 @@
       <c r="A410" t="n">
         <v>409</v>
       </c>
-      <c r="B410" s="1" t="n">
+      <c r="B410" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C410" t="inlineStr">
@@ -12323,7 +12323,7 @@
       <c r="A411" t="n">
         <v>410</v>
       </c>
-      <c r="B411" s="1" t="n">
+      <c r="B411" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C411" t="inlineStr">
@@ -12352,7 +12352,7 @@
       <c r="A412" t="n">
         <v>411</v>
       </c>
-      <c r="B412" s="1" t="n">
+      <c r="B412" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C412" t="inlineStr">
@@ -12381,7 +12381,7 @@
       <c r="A413" t="n">
         <v>412</v>
       </c>
-      <c r="B413" s="1" t="n">
+      <c r="B413" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C413" t="inlineStr">
@@ -12410,7 +12410,7 @@
       <c r="A414" t="n">
         <v>413</v>
       </c>
-      <c r="B414" s="1" t="n">
+      <c r="B414" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C414" t="inlineStr">
@@ -12439,7 +12439,7 @@
       <c r="A415" t="n">
         <v>414</v>
       </c>
-      <c r="B415" s="1" t="n">
+      <c r="B415" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C415" t="inlineStr">
@@ -12468,7 +12468,7 @@
       <c r="A416" t="n">
         <v>415</v>
       </c>
-      <c r="B416" s="1" t="n">
+      <c r="B416" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C416" t="inlineStr">
@@ -12497,7 +12497,7 @@
       <c r="A417" t="n">
         <v>416</v>
       </c>
-      <c r="B417" s="1" t="n">
+      <c r="B417" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C417" t="inlineStr">
@@ -12526,7 +12526,7 @@
       <c r="A418" t="n">
         <v>417</v>
       </c>
-      <c r="B418" s="1" t="n">
+      <c r="B418" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C418" t="inlineStr">
@@ -12555,7 +12555,7 @@
       <c r="A419" t="n">
         <v>418</v>
       </c>
-      <c r="B419" s="1" t="n">
+      <c r="B419" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C419" t="inlineStr">
@@ -12584,7 +12584,7 @@
       <c r="A420" t="n">
         <v>419</v>
       </c>
-      <c r="B420" s="1" t="n">
+      <c r="B420" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C420" t="inlineStr">
@@ -12613,7 +12613,7 @@
       <c r="A421" t="n">
         <v>420</v>
       </c>
-      <c r="B421" s="1" t="n">
+      <c r="B421" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C421" t="inlineStr">
@@ -12642,7 +12642,7 @@
       <c r="A422" t="n">
         <v>421</v>
       </c>
-      <c r="B422" s="1" t="n">
+      <c r="B422" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C422" t="inlineStr">
@@ -12671,7 +12671,7 @@
       <c r="A423" t="n">
         <v>422</v>
       </c>
-      <c r="B423" s="1" t="n">
+      <c r="B423" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C423" t="inlineStr">
@@ -12700,7 +12700,7 @@
       <c r="A424" t="n">
         <v>423</v>
       </c>
-      <c r="B424" s="1" t="n">
+      <c r="B424" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C424" t="inlineStr">
@@ -12729,7 +12729,7 @@
       <c r="A425" t="n">
         <v>424</v>
       </c>
-      <c r="B425" s="1" t="n">
+      <c r="B425" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C425" t="inlineStr">
@@ -12758,7 +12758,7 @@
       <c r="A426" t="n">
         <v>425</v>
       </c>
-      <c r="B426" s="1" t="n">
+      <c r="B426" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C426" t="inlineStr">
@@ -12787,7 +12787,7 @@
       <c r="A427" t="n">
         <v>426</v>
       </c>
-      <c r="B427" s="1" t="n">
+      <c r="B427" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C427" t="inlineStr">
@@ -12816,7 +12816,7 @@
       <c r="A428" t="n">
         <v>427</v>
       </c>
-      <c r="B428" s="1" t="n">
+      <c r="B428" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C428" t="inlineStr">
@@ -12845,7 +12845,7 @@
       <c r="A429" t="n">
         <v>428</v>
       </c>
-      <c r="B429" s="1" t="n">
+      <c r="B429" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C429" t="inlineStr">
@@ -12874,7 +12874,7 @@
       <c r="A430" t="n">
         <v>429</v>
       </c>
-      <c r="B430" s="1" t="n">
+      <c r="B430" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C430" t="inlineStr">
@@ -12903,7 +12903,7 @@
       <c r="A431" t="n">
         <v>430</v>
       </c>
-      <c r="B431" s="1" t="n">
+      <c r="B431" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C431" t="inlineStr">
@@ -12932,7 +12932,7 @@
       <c r="A432" t="n">
         <v>431</v>
       </c>
-      <c r="B432" s="1" t="n">
+      <c r="B432" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C432" t="inlineStr">
@@ -12961,7 +12961,7 @@
       <c r="A433" t="n">
         <v>432</v>
       </c>
-      <c r="B433" s="1" t="n">
+      <c r="B433" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C433" t="inlineStr">
@@ -12990,7 +12990,7 @@
       <c r="A434" t="n">
         <v>433</v>
       </c>
-      <c r="B434" s="1" t="n">
+      <c r="B434" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C434" t="inlineStr">
@@ -13019,7 +13019,7 @@
       <c r="A435" t="n">
         <v>434</v>
       </c>
-      <c r="B435" s="1" t="n">
+      <c r="B435" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C435" t="inlineStr">
@@ -13048,7 +13048,7 @@
       <c r="A436" t="n">
         <v>435</v>
       </c>
-      <c r="B436" s="1" t="n">
+      <c r="B436" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C436" t="inlineStr">
@@ -13077,7 +13077,7 @@
       <c r="A437" t="n">
         <v>436</v>
       </c>
-      <c r="B437" s="1" t="n">
+      <c r="B437" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C437" t="inlineStr">
@@ -13106,7 +13106,7 @@
       <c r="A438" t="n">
         <v>437</v>
       </c>
-      <c r="B438" s="1" t="n">
+      <c r="B438" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C438" t="inlineStr">
@@ -13135,7 +13135,7 @@
       <c r="A439" t="n">
         <v>438</v>
       </c>
-      <c r="B439" s="1" t="n">
+      <c r="B439" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C439" t="inlineStr">
@@ -13164,7 +13164,7 @@
       <c r="A440" t="n">
         <v>439</v>
       </c>
-      <c r="B440" s="1" t="n">
+      <c r="B440" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C440" t="inlineStr">
@@ -13193,7 +13193,7 @@
       <c r="A441" t="n">
         <v>440</v>
       </c>
-      <c r="B441" s="1" t="n">
+      <c r="B441" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C441" t="inlineStr">
@@ -13222,7 +13222,7 @@
       <c r="A442" t="n">
         <v>441</v>
       </c>
-      <c r="B442" s="1" t="n">
+      <c r="B442" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C442" t="inlineStr">
@@ -13251,7 +13251,7 @@
       <c r="A443" t="n">
         <v>442</v>
       </c>
-      <c r="B443" s="1" t="n">
+      <c r="B443" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C443" t="inlineStr">
@@ -13280,7 +13280,7 @@
       <c r="A444" t="n">
         <v>443</v>
       </c>
-      <c r="B444" s="1" t="n">
+      <c r="B444" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C444" t="inlineStr">
@@ -13309,7 +13309,7 @@
       <c r="A445" t="n">
         <v>444</v>
       </c>
-      <c r="B445" s="1" t="n">
+      <c r="B445" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C445" t="inlineStr">
@@ -13338,7 +13338,7 @@
       <c r="A446" t="n">
         <v>445</v>
       </c>
-      <c r="B446" s="1" t="n">
+      <c r="B446" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C446" t="inlineStr">
@@ -13367,7 +13367,7 @@
       <c r="A447" t="n">
         <v>446</v>
       </c>
-      <c r="B447" s="1" t="n">
+      <c r="B447" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C447" t="inlineStr">
@@ -13396,7 +13396,7 @@
       <c r="A448" t="n">
         <v>447</v>
       </c>
-      <c r="B448" s="1" t="n">
+      <c r="B448" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C448" t="inlineStr">
@@ -13425,7 +13425,7 @@
       <c r="A449" t="n">
         <v>448</v>
       </c>
-      <c r="B449" s="1" t="n">
+      <c r="B449" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C449" t="inlineStr">
@@ -13454,7 +13454,7 @@
       <c r="A450" t="n">
         <v>449</v>
       </c>
-      <c r="B450" s="1" t="n">
+      <c r="B450" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C450" t="inlineStr">
@@ -13483,7 +13483,7 @@
       <c r="A451" t="n">
         <v>450</v>
       </c>
-      <c r="B451" s="1" t="n">
+      <c r="B451" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C451" t="inlineStr">
@@ -13512,7 +13512,7 @@
       <c r="A452" t="n">
         <v>451</v>
       </c>
-      <c r="B452" s="1" t="n">
+      <c r="B452" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C452" t="inlineStr">
@@ -13541,7 +13541,7 @@
       <c r="A453" t="n">
         <v>452</v>
       </c>
-      <c r="B453" s="1" t="n">
+      <c r="B453" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C453" t="inlineStr">
@@ -13570,7 +13570,7 @@
       <c r="A454" t="n">
         <v>453</v>
       </c>
-      <c r="B454" s="1" t="n">
+      <c r="B454" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C454" t="inlineStr">
@@ -13599,7 +13599,7 @@
       <c r="A455" t="n">
         <v>454</v>
       </c>
-      <c r="B455" s="1" t="n">
+      <c r="B455" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C455" t="inlineStr">
@@ -13628,7 +13628,7 @@
       <c r="A456" t="n">
         <v>455</v>
       </c>
-      <c r="B456" s="1" t="n">
+      <c r="B456" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C456" t="inlineStr">
@@ -13657,7 +13657,7 @@
       <c r="A457" t="n">
         <v>456</v>
       </c>
-      <c r="B457" s="1" t="n">
+      <c r="B457" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C457" t="inlineStr">
@@ -13686,7 +13686,7 @@
       <c r="A458" t="n">
         <v>457</v>
       </c>
-      <c r="B458" s="1" t="n">
+      <c r="B458" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C458" t="inlineStr">
@@ -13715,7 +13715,7 @@
       <c r="A459" t="n">
         <v>458</v>
       </c>
-      <c r="B459" s="1" t="n">
+      <c r="B459" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C459" t="inlineStr">
@@ -13744,7 +13744,7 @@
       <c r="A460" t="n">
         <v>459</v>
       </c>
-      <c r="B460" s="1" t="n">
+      <c r="B460" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C460" t="inlineStr">
@@ -13773,7 +13773,7 @@
       <c r="A461" t="n">
         <v>460</v>
       </c>
-      <c r="B461" s="1" t="n">
+      <c r="B461" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C461" t="inlineStr">
@@ -13802,7 +13802,7 @@
       <c r="A462" t="n">
         <v>461</v>
       </c>
-      <c r="B462" s="1" t="n">
+      <c r="B462" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C462" t="inlineStr">
@@ -13831,7 +13831,7 @@
       <c r="A463" t="n">
         <v>462</v>
       </c>
-      <c r="B463" s="1" t="n">
+      <c r="B463" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C463" t="inlineStr">
@@ -13860,7 +13860,7 @@
       <c r="A464" t="n">
         <v>463</v>
       </c>
-      <c r="B464" s="1" t="n">
+      <c r="B464" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C464" t="inlineStr">
@@ -13889,7 +13889,7 @@
       <c r="A465" t="n">
         <v>464</v>
       </c>
-      <c r="B465" s="1" t="n">
+      <c r="B465" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C465" t="inlineStr">
@@ -13918,7 +13918,7 @@
       <c r="A466" t="n">
         <v>465</v>
       </c>
-      <c r="B466" s="1" t="n">
+      <c r="B466" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C466" t="inlineStr">
@@ -13947,7 +13947,7 @@
       <c r="A467" t="n">
         <v>466</v>
       </c>
-      <c r="B467" s="1" t="n">
+      <c r="B467" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C467" t="inlineStr">
@@ -13976,7 +13976,7 @@
       <c r="A468" t="n">
         <v>467</v>
       </c>
-      <c r="B468" s="1" t="n">
+      <c r="B468" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C468" t="inlineStr">
@@ -14005,7 +14005,7 @@
       <c r="A469" t="n">
         <v>468</v>
       </c>
-      <c r="B469" s="1" t="n">
+      <c r="B469" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C469" t="inlineStr">
@@ -14034,7 +14034,7 @@
       <c r="A470" t="n">
         <v>469</v>
       </c>
-      <c r="B470" s="1" t="n">
+      <c r="B470" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C470" t="inlineStr">
@@ -14063,7 +14063,7 @@
       <c r="A471" t="n">
         <v>470</v>
       </c>
-      <c r="B471" s="1" t="n">
+      <c r="B471" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C471" t="inlineStr">
@@ -14092,7 +14092,7 @@
       <c r="A472" t="n">
         <v>471</v>
       </c>
-      <c r="B472" s="1" t="n">
+      <c r="B472" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C472" t="inlineStr">
@@ -14121,7 +14121,7 @@
       <c r="A473" t="n">
         <v>472</v>
       </c>
-      <c r="B473" s="1" t="n">
+      <c r="B473" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C473" t="inlineStr">
@@ -14150,7 +14150,7 @@
       <c r="A474" t="n">
         <v>473</v>
       </c>
-      <c r="B474" s="1" t="n">
+      <c r="B474" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C474" t="inlineStr">
@@ -14179,7 +14179,7 @@
       <c r="A475" t="n">
         <v>474</v>
       </c>
-      <c r="B475" s="1" t="n">
+      <c r="B475" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C475" t="inlineStr">
@@ -14208,7 +14208,7 @@
       <c r="A476" t="n">
         <v>475</v>
       </c>
-      <c r="B476" s="1" t="n">
+      <c r="B476" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C476" t="inlineStr">
@@ -14237,7 +14237,7 @@
       <c r="A477" t="n">
         <v>476</v>
       </c>
-      <c r="B477" s="1" t="n">
+      <c r="B477" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C477" t="inlineStr">
@@ -14266,7 +14266,7 @@
       <c r="A478" t="n">
         <v>477</v>
       </c>
-      <c r="B478" s="1" t="n">
+      <c r="B478" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C478" t="inlineStr">
@@ -14295,7 +14295,7 @@
       <c r="A479" t="n">
         <v>478</v>
       </c>
-      <c r="B479" s="1" t="n">
+      <c r="B479" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C479" t="inlineStr">
@@ -14324,7 +14324,7 @@
       <c r="A480" t="n">
         <v>479</v>
       </c>
-      <c r="B480" s="1" t="n">
+      <c r="B480" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C480" t="inlineStr">
@@ -14353,7 +14353,7 @@
       <c r="A481" t="n">
         <v>480</v>
       </c>
-      <c r="B481" s="1" t="n">
+      <c r="B481" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C481" t="inlineStr">
@@ -14382,7 +14382,7 @@
       <c r="A482" t="n">
         <v>481</v>
       </c>
-      <c r="B482" s="1" t="n">
+      <c r="B482" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C482" t="inlineStr">
@@ -14411,7 +14411,7 @@
       <c r="A483" t="n">
         <v>482</v>
       </c>
-      <c r="B483" s="1" t="n">
+      <c r="B483" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C483" t="inlineStr">
@@ -14440,7 +14440,7 @@
       <c r="A484" t="n">
         <v>483</v>
       </c>
-      <c r="B484" s="1" t="n">
+      <c r="B484" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C484" t="inlineStr">
@@ -14469,7 +14469,7 @@
       <c r="A485" t="n">
         <v>484</v>
       </c>
-      <c r="B485" s="1" t="n">
+      <c r="B485" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C485" t="inlineStr">
@@ -14498,7 +14498,7 @@
       <c r="A486" t="n">
         <v>485</v>
       </c>
-      <c r="B486" s="1" t="n">
+      <c r="B486" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C486" t="inlineStr">
@@ -14527,7 +14527,7 @@
       <c r="A487" t="n">
         <v>486</v>
       </c>
-      <c r="B487" s="1" t="n">
+      <c r="B487" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C487" t="inlineStr">
@@ -14556,7 +14556,7 @@
       <c r="A488" t="n">
         <v>487</v>
       </c>
-      <c r="B488" s="1" t="n">
+      <c r="B488" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C488" t="inlineStr">
@@ -14585,7 +14585,7 @@
       <c r="A489" t="n">
         <v>488</v>
       </c>
-      <c r="B489" s="1" t="n">
+      <c r="B489" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C489" t="inlineStr">
@@ -14614,7 +14614,7 @@
       <c r="A490" t="n">
         <v>489</v>
       </c>
-      <c r="B490" s="1" t="n">
+      <c r="B490" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C490" t="inlineStr">
@@ -14643,7 +14643,7 @@
       <c r="A491" t="n">
         <v>490</v>
       </c>
-      <c r="B491" s="1" t="n">
+      <c r="B491" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C491" t="inlineStr">
@@ -14672,7 +14672,7 @@
       <c r="A492" t="n">
         <v>491</v>
       </c>
-      <c r="B492" s="1" t="n">
+      <c r="B492" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C492" t="inlineStr">
@@ -14701,7 +14701,7 @@
       <c r="A493" t="n">
         <v>492</v>
       </c>
-      <c r="B493" s="1" t="n">
+      <c r="B493" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C493" t="inlineStr">
@@ -14730,7 +14730,7 @@
       <c r="A494" t="n">
         <v>493</v>
       </c>
-      <c r="B494" s="1" t="n">
+      <c r="B494" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C494" t="inlineStr">
@@ -14759,7 +14759,7 @@
       <c r="A495" t="n">
         <v>494</v>
       </c>
-      <c r="B495" s="1" t="n">
+      <c r="B495" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C495" t="inlineStr">
@@ -14788,7 +14788,7 @@
       <c r="A496" t="n">
         <v>495</v>
       </c>
-      <c r="B496" s="1" t="n">
+      <c r="B496" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C496" t="inlineStr">
@@ -14817,7 +14817,7 @@
       <c r="A497" t="n">
         <v>496</v>
       </c>
-      <c r="B497" s="1" t="n">
+      <c r="B497" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C497" t="inlineStr">
@@ -14846,7 +14846,7 @@
       <c r="A498" t="n">
         <v>497</v>
       </c>
-      <c r="B498" s="1" t="n">
+      <c r="B498" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C498" t="inlineStr">
@@ -14875,7 +14875,7 @@
       <c r="A499" t="n">
         <v>498</v>
       </c>
-      <c r="B499" s="1" t="n">
+      <c r="B499" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C499" t="inlineStr">
@@ -14904,7 +14904,7 @@
       <c r="A500" t="n">
         <v>499</v>
       </c>
-      <c r="B500" s="1" t="n">
+      <c r="B500" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C500" t="inlineStr">
@@ -14933,7 +14933,7 @@
       <c r="A501" t="n">
         <v>500</v>
       </c>
-      <c r="B501" s="1" t="n">
+      <c r="B501" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C501" t="inlineStr">
@@ -14962,7 +14962,7 @@
       <c r="A502" t="n">
         <v>501</v>
       </c>
-      <c r="B502" s="1" t="n">
+      <c r="B502" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C502" t="inlineStr">
@@ -14991,7 +14991,7 @@
       <c r="A503" t="n">
         <v>502</v>
       </c>
-      <c r="B503" s="1" t="n">
+      <c r="B503" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C503" t="inlineStr">
@@ -15020,7 +15020,7 @@
       <c r="A504" t="n">
         <v>503</v>
       </c>
-      <c r="B504" s="1" t="n">
+      <c r="B504" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C504" t="inlineStr">
@@ -15049,7 +15049,7 @@
       <c r="A505" t="n">
         <v>504</v>
       </c>
-      <c r="B505" s="1" t="n">
+      <c r="B505" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C505" t="inlineStr">
@@ -15078,7 +15078,7 @@
       <c r="A506" t="n">
         <v>505</v>
       </c>
-      <c r="B506" s="1" t="n">
+      <c r="B506" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C506" t="inlineStr">
@@ -15107,7 +15107,7 @@
       <c r="A507" t="n">
         <v>506</v>
       </c>
-      <c r="B507" s="1" t="n">
+      <c r="B507" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C507" t="inlineStr">
@@ -15136,7 +15136,7 @@
       <c r="A508" t="n">
         <v>507</v>
       </c>
-      <c r="B508" s="1" t="n">
+      <c r="B508" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C508" t="inlineStr">
@@ -15165,7 +15165,7 @@
       <c r="A509" t="n">
         <v>508</v>
       </c>
-      <c r="B509" s="1" t="n">
+      <c r="B509" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C509" t="inlineStr">
@@ -15194,7 +15194,7 @@
       <c r="A510" t="n">
         <v>509</v>
       </c>
-      <c r="B510" s="1" t="n">
+      <c r="B510" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C510" t="inlineStr">
@@ -15223,7 +15223,7 @@
       <c r="A511" t="n">
         <v>510</v>
       </c>
-      <c r="B511" s="1" t="n">
+      <c r="B511" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C511" t="inlineStr">
@@ -15252,7 +15252,7 @@
       <c r="A512" t="n">
         <v>511</v>
       </c>
-      <c r="B512" s="1" t="n">
+      <c r="B512" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C512" t="inlineStr">
@@ -15281,7 +15281,7 @@
       <c r="A513" t="n">
         <v>512</v>
       </c>
-      <c r="B513" s="1" t="n">
+      <c r="B513" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C513" t="inlineStr">
@@ -15310,7 +15310,7 @@
       <c r="A514" t="n">
         <v>513</v>
       </c>
-      <c r="B514" s="1" t="n">
+      <c r="B514" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C514" t="inlineStr">
@@ -15339,7 +15339,7 @@
       <c r="A515" t="n">
         <v>514</v>
       </c>
-      <c r="B515" s="1" t="n">
+      <c r="B515" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C515" t="inlineStr">
@@ -15368,7 +15368,7 @@
       <c r="A516" t="n">
         <v>515</v>
       </c>
-      <c r="B516" s="1" t="n">
+      <c r="B516" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C516" t="inlineStr">
@@ -15397,7 +15397,7 @@
       <c r="A517" t="n">
         <v>516</v>
       </c>
-      <c r="B517" s="1" t="n">
+      <c r="B517" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C517" t="inlineStr">
@@ -15426,7 +15426,7 @@
       <c r="A518" t="n">
         <v>517</v>
       </c>
-      <c r="B518" s="1" t="n">
+      <c r="B518" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C518" t="inlineStr">
@@ -15455,7 +15455,7 @@
       <c r="A519" t="n">
         <v>518</v>
       </c>
-      <c r="B519" s="1" t="n">
+      <c r="B519" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C519" t="inlineStr">
@@ -15484,7 +15484,7 @@
       <c r="A520" t="n">
         <v>519</v>
       </c>
-      <c r="B520" s="1" t="n">
+      <c r="B520" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C520" t="inlineStr">
@@ -15513,7 +15513,7 @@
       <c r="A521" t="n">
         <v>520</v>
       </c>
-      <c r="B521" s="1" t="n">
+      <c r="B521" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C521" t="inlineStr">
@@ -15542,7 +15542,7 @@
       <c r="A522" t="n">
         <v>521</v>
       </c>
-      <c r="B522" s="1" t="n">
+      <c r="B522" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C522" t="inlineStr">
@@ -15571,7 +15571,7 @@
       <c r="A523" t="n">
         <v>522</v>
       </c>
-      <c r="B523" s="1" t="n">
+      <c r="B523" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C523" t="inlineStr">
@@ -15600,7 +15600,7 @@
       <c r="A524" t="n">
         <v>523</v>
       </c>
-      <c r="B524" s="1" t="n">
+      <c r="B524" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C524" t="inlineStr">
@@ -15629,7 +15629,7 @@
       <c r="A525" t="n">
         <v>524</v>
       </c>
-      <c r="B525" s="1" t="n">
+      <c r="B525" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C525" t="inlineStr">
@@ -15658,7 +15658,7 @@
       <c r="A526" t="n">
         <v>525</v>
       </c>
-      <c r="B526" s="1" t="n">
+      <c r="B526" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C526" t="inlineStr">
@@ -15687,7 +15687,7 @@
       <c r="A527" t="n">
         <v>526</v>
       </c>
-      <c r="B527" s="1" t="n">
+      <c r="B527" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C527" t="inlineStr">
@@ -15716,7 +15716,7 @@
       <c r="A528" t="n">
         <v>527</v>
       </c>
-      <c r="B528" s="1" t="n">
+      <c r="B528" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C528" t="inlineStr">
@@ -15745,7 +15745,7 @@
       <c r="A529" t="n">
         <v>528</v>
       </c>
-      <c r="B529" s="1" t="n">
+      <c r="B529" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C529" t="inlineStr">
@@ -15774,7 +15774,7 @@
       <c r="A530" t="n">
         <v>529</v>
       </c>
-      <c r="B530" s="1" t="n">
+      <c r="B530" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C530" t="inlineStr">
@@ -15803,7 +15803,7 @@
       <c r="A531" t="n">
         <v>530</v>
       </c>
-      <c r="B531" s="1" t="n">
+      <c r="B531" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C531" t="inlineStr">
@@ -15832,7 +15832,7 @@
       <c r="A532" t="n">
         <v>531</v>
       </c>
-      <c r="B532" s="1" t="n">
+      <c r="B532" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C532" t="inlineStr">
@@ -15861,7 +15861,7 @@
       <c r="A533" t="n">
         <v>532</v>
       </c>
-      <c r="B533" s="1" t="n">
+      <c r="B533" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C533" t="inlineStr">
@@ -15890,7 +15890,7 @@
       <c r="A534" t="n">
         <v>533</v>
       </c>
-      <c r="B534" s="1" t="n">
+      <c r="B534" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C534" t="inlineStr">
@@ -15919,7 +15919,7 @@
       <c r="A535" t="n">
         <v>534</v>
       </c>
-      <c r="B535" s="1" t="n">
+      <c r="B535" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C535" t="inlineStr">
@@ -15948,7 +15948,7 @@
       <c r="A536" t="n">
         <v>535</v>
       </c>
-      <c r="B536" s="1" t="n">
+      <c r="B536" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C536" t="inlineStr">
@@ -15977,7 +15977,7 @@
       <c r="A537" t="n">
         <v>536</v>
       </c>
-      <c r="B537" s="1" t="n">
+      <c r="B537" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C537" t="inlineStr">
@@ -16006,7 +16006,7 @@
       <c r="A538" t="n">
         <v>537</v>
       </c>
-      <c r="B538" s="1" t="n">
+      <c r="B538" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C538" t="inlineStr">
@@ -16035,7 +16035,7 @@
       <c r="A539" t="n">
         <v>538</v>
       </c>
-      <c r="B539" s="1" t="n">
+      <c r="B539" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C539" t="inlineStr">
@@ -16064,7 +16064,7 @@
       <c r="A540" t="n">
         <v>539</v>
       </c>
-      <c r="B540" s="1" t="n">
+      <c r="B540" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C540" t="inlineStr">
@@ -16093,7 +16093,7 @@
       <c r="A541" t="n">
         <v>540</v>
       </c>
-      <c r="B541" s="1" t="n">
+      <c r="B541" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C541" t="inlineStr">
@@ -16122,7 +16122,7 @@
       <c r="A542" t="n">
         <v>541</v>
       </c>
-      <c r="B542" s="1" t="n">
+      <c r="B542" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C542" t="inlineStr">
@@ -16151,7 +16151,7 @@
       <c r="A543" t="n">
         <v>542</v>
       </c>
-      <c r="B543" s="1" t="n">
+      <c r="B543" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C543" t="inlineStr">
@@ -16180,7 +16180,7 @@
       <c r="A544" t="n">
         <v>543</v>
       </c>
-      <c r="B544" s="1" t="n">
+      <c r="B544" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C544" t="inlineStr">
@@ -16209,7 +16209,7 @@
       <c r="A545" t="n">
         <v>544</v>
       </c>
-      <c r="B545" s="1" t="n">
+      <c r="B545" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C545" t="inlineStr">
@@ -16238,7 +16238,7 @@
       <c r="A546" t="n">
         <v>545</v>
       </c>
-      <c r="B546" s="1" t="n">
+      <c r="B546" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C546" t="inlineStr">
@@ -16267,7 +16267,7 @@
       <c r="A547" t="n">
         <v>546</v>
       </c>
-      <c r="B547" s="1" t="n">
+      <c r="B547" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C547" t="inlineStr">
@@ -16296,7 +16296,7 @@
       <c r="A548" t="n">
         <v>547</v>
       </c>
-      <c r="B548" s="1" t="n">
+      <c r="B548" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C548" t="inlineStr">
@@ -16325,7 +16325,7 @@
       <c r="A549" t="n">
         <v>548</v>
       </c>
-      <c r="B549" s="1" t="n">
+      <c r="B549" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C549" t="inlineStr">
@@ -16354,7 +16354,7 @@
       <c r="A550" t="n">
         <v>549</v>
       </c>
-      <c r="B550" s="1" t="n">
+      <c r="B550" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C550" t="inlineStr">
@@ -16383,7 +16383,7 @@
       <c r="A551" t="n">
         <v>550</v>
       </c>
-      <c r="B551" s="1" t="n">
+      <c r="B551" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C551" t="inlineStr">
@@ -16412,7 +16412,7 @@
       <c r="A552" t="n">
         <v>551</v>
       </c>
-      <c r="B552" s="1" t="n">
+      <c r="B552" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C552" t="inlineStr">
@@ -16441,7 +16441,7 @@
       <c r="A553" t="n">
         <v>552</v>
       </c>
-      <c r="B553" s="1" t="n">
+      <c r="B553" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C553" t="inlineStr">
@@ -16470,7 +16470,7 @@
       <c r="A554" t="n">
         <v>553</v>
       </c>
-      <c r="B554" s="1" t="n">
+      <c r="B554" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C554" t="inlineStr">
@@ -16499,7 +16499,7 @@
       <c r="A555" t="n">
         <v>554</v>
       </c>
-      <c r="B555" s="1" t="n">
+      <c r="B555" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C555" t="inlineStr">
@@ -16528,7 +16528,7 @@
       <c r="A556" t="n">
         <v>555</v>
       </c>
-      <c r="B556" s="1" t="n">
+      <c r="B556" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C556" t="inlineStr">
@@ -16557,7 +16557,7 @@
       <c r="A557" t="n">
         <v>556</v>
       </c>
-      <c r="B557" s="1" t="n">
+      <c r="B557" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C557" t="inlineStr">
@@ -16586,7 +16586,7 @@
       <c r="A558" t="n">
         <v>557</v>
       </c>
-      <c r="B558" s="1" t="n">
+      <c r="B558" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C558" t="inlineStr">
@@ -16615,7 +16615,7 @@
       <c r="A559" t="n">
         <v>558</v>
       </c>
-      <c r="B559" s="1" t="n">
+      <c r="B559" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C559" t="inlineStr">
@@ -16644,7 +16644,7 @@
       <c r="A560" t="n">
         <v>559</v>
       </c>
-      <c r="B560" s="1" t="n">
+      <c r="B560" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C560" t="inlineStr">
@@ -16673,7 +16673,7 @@
       <c r="A561" t="n">
         <v>560</v>
       </c>
-      <c r="B561" s="1" t="n">
+      <c r="B561" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C561" t="inlineStr">
@@ -16702,7 +16702,7 @@
       <c r="A562" t="n">
         <v>561</v>
       </c>
-      <c r="B562" s="1" t="n">
+      <c r="B562" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C562" t="inlineStr">
@@ -16731,7 +16731,7 @@
       <c r="A563" t="n">
         <v>562</v>
       </c>
-      <c r="B563" s="1" t="n">
+      <c r="B563" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C563" t="inlineStr">
@@ -16760,7 +16760,7 @@
       <c r="A564" t="n">
         <v>563</v>
       </c>
-      <c r="B564" s="1" t="n">
+      <c r="B564" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C564" t="inlineStr">
@@ -16789,7 +16789,7 @@
       <c r="A565" t="n">
         <v>564</v>
       </c>
-      <c r="B565" s="1" t="n">
+      <c r="B565" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C565" t="inlineStr">
@@ -16818,7 +16818,7 @@
       <c r="A566" t="n">
         <v>565</v>
       </c>
-      <c r="B566" s="1" t="n">
+      <c r="B566" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C566" t="inlineStr">
@@ -16847,7 +16847,7 @@
       <c r="A567" t="n">
         <v>566</v>
       </c>
-      <c r="B567" s="1" t="n">
+      <c r="B567" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C567" t="inlineStr">
@@ -16876,7 +16876,7 @@
       <c r="A568" t="n">
         <v>567</v>
       </c>
-      <c r="B568" s="1" t="n">
+      <c r="B568" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C568" t="inlineStr">
@@ -16905,7 +16905,7 @@
       <c r="A569" t="n">
         <v>568</v>
       </c>
-      <c r="B569" s="1" t="n">
+      <c r="B569" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C569" t="inlineStr">
@@ -16934,7 +16934,7 @@
       <c r="A570" t="n">
         <v>569</v>
       </c>
-      <c r="B570" s="1" t="n">
+      <c r="B570" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C570" t="inlineStr">
@@ -16963,7 +16963,7 @@
       <c r="A571" t="n">
         <v>570</v>
       </c>
-      <c r="B571" s="1" t="n">
+      <c r="B571" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C571" t="inlineStr">
@@ -16992,7 +16992,7 @@
       <c r="A572" t="n">
         <v>571</v>
       </c>
-      <c r="B572" s="1" t="n">
+      <c r="B572" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C572" t="inlineStr">
@@ -17021,7 +17021,7 @@
       <c r="A573" t="n">
         <v>572</v>
       </c>
-      <c r="B573" s="1" t="n">
+      <c r="B573" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C573" t="inlineStr">
@@ -17050,7 +17050,7 @@
       <c r="A574" t="n">
         <v>573</v>
       </c>
-      <c r="B574" s="1" t="n">
+      <c r="B574" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C574" t="inlineStr">
@@ -17079,7 +17079,7 @@
       <c r="A575" t="n">
         <v>574</v>
       </c>
-      <c r="B575" s="1" t="n">
+      <c r="B575" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C575" t="inlineStr">
@@ -17108,7 +17108,7 @@
       <c r="A576" t="n">
         <v>575</v>
       </c>
-      <c r="B576" s="1" t="n">
+      <c r="B576" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C576" t="inlineStr">
@@ -17137,7 +17137,7 @@
       <c r="A577" t="n">
         <v>576</v>
       </c>
-      <c r="B577" s="1" t="n">
+      <c r="B577" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C577" t="inlineStr">
@@ -17166,7 +17166,7 @@
       <c r="A578" t="n">
         <v>577</v>
       </c>
-      <c r="B578" s="1" t="n">
+      <c r="B578" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C578" t="inlineStr">
@@ -17195,7 +17195,7 @@
       <c r="A579" t="n">
         <v>578</v>
       </c>
-      <c r="B579" s="1" t="n">
+      <c r="B579" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C579" t="inlineStr">
@@ -17224,7 +17224,7 @@
       <c r="A580" t="n">
         <v>579</v>
       </c>
-      <c r="B580" s="1" t="n">
+      <c r="B580" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C580" t="inlineStr">
@@ -17253,7 +17253,7 @@
       <c r="A581" t="n">
         <v>580</v>
       </c>
-      <c r="B581" s="1" t="n">
+      <c r="B581" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C581" t="inlineStr">
@@ -17282,7 +17282,7 @@
       <c r="A582" t="n">
         <v>581</v>
       </c>
-      <c r="B582" s="1" t="n">
+      <c r="B582" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C582" t="inlineStr">
@@ -17311,7 +17311,7 @@
       <c r="A583" t="n">
         <v>582</v>
       </c>
-      <c r="B583" s="1" t="n">
+      <c r="B583" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C583" t="inlineStr">
@@ -17340,7 +17340,7 @@
       <c r="A584" t="n">
         <v>583</v>
       </c>
-      <c r="B584" s="1" t="n">
+      <c r="B584" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C584" t="inlineStr">
@@ -17369,7 +17369,7 @@
       <c r="A585" t="n">
         <v>584</v>
       </c>
-      <c r="B585" s="1" t="n">
+      <c r="B585" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C585" t="inlineStr">
@@ -17398,7 +17398,7 @@
       <c r="A586" t="n">
         <v>585</v>
       </c>
-      <c r="B586" s="1" t="n">
+      <c r="B586" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C586" t="inlineStr">
@@ -17427,7 +17427,7 @@
       <c r="A587" t="n">
         <v>586</v>
       </c>
-      <c r="B587" s="1" t="n">
+      <c r="B587" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C587" t="inlineStr">
@@ -17456,7 +17456,7 @@
       <c r="A588" t="n">
         <v>587</v>
       </c>
-      <c r="B588" s="1" t="n">
+      <c r="B588" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C588" t="inlineStr">
@@ -17485,7 +17485,7 @@
       <c r="A589" t="n">
         <v>588</v>
       </c>
-      <c r="B589" s="1" t="n">
+      <c r="B589" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C589" t="inlineStr">
@@ -17514,7 +17514,7 @@
       <c r="A590" t="n">
         <v>589</v>
       </c>
-      <c r="B590" s="1" t="n">
+      <c r="B590" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C590" t="inlineStr">
@@ -17543,7 +17543,7 @@
       <c r="A591" t="n">
         <v>590</v>
       </c>
-      <c r="B591" s="1" t="n">
+      <c r="B591" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C591" t="inlineStr">
@@ -17572,7 +17572,7 @@
       <c r="A592" t="n">
         <v>591</v>
       </c>
-      <c r="B592" s="1" t="n">
+      <c r="B592" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C592" t="inlineStr">
@@ -17601,7 +17601,7 @@
       <c r="A593" t="n">
         <v>592</v>
       </c>
-      <c r="B593" s="1" t="n">
+      <c r="B593" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C593" t="inlineStr">
@@ -17630,7 +17630,7 @@
       <c r="A594" t="n">
         <v>593</v>
       </c>
-      <c r="B594" s="1" t="n">
+      <c r="B594" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C594" t="inlineStr">
@@ -17659,7 +17659,7 @@
       <c r="A595" t="n">
         <v>594</v>
       </c>
-      <c r="B595" s="1" t="n">
+      <c r="B595" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C595" t="inlineStr">
@@ -17688,7 +17688,7 @@
       <c r="A596" t="n">
         <v>595</v>
       </c>
-      <c r="B596" s="1" t="n">
+      <c r="B596" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C596" t="inlineStr">
@@ -17717,7 +17717,7 @@
       <c r="A597" t="n">
         <v>596</v>
       </c>
-      <c r="B597" s="1" t="n">
+      <c r="B597" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C597" t="inlineStr">
@@ -17746,7 +17746,7 @@
       <c r="A598" t="n">
         <v>597</v>
       </c>
-      <c r="B598" s="1" t="n">
+      <c r="B598" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C598" t="inlineStr">
@@ -17775,7 +17775,7 @@
       <c r="A599" t="n">
         <v>598</v>
       </c>
-      <c r="B599" s="1" t="n">
+      <c r="B599" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C599" t="inlineStr">
@@ -17804,7 +17804,7 @@
       <c r="A600" t="n">
         <v>599</v>
       </c>
-      <c r="B600" s="1" t="n">
+      <c r="B600" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C600" t="inlineStr">
@@ -17833,7 +17833,7 @@
       <c r="A601" t="n">
         <v>600</v>
       </c>
-      <c r="B601" s="1" t="n">
+      <c r="B601" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C601" t="inlineStr">
@@ -17862,7 +17862,7 @@
       <c r="A602" t="n">
         <v>601</v>
       </c>
-      <c r="B602" s="1" t="n">
+      <c r="B602" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C602" t="inlineStr">
@@ -17891,7 +17891,7 @@
       <c r="A603" t="n">
         <v>602</v>
       </c>
-      <c r="B603" s="1" t="n">
+      <c r="B603" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C603" t="inlineStr">
@@ -17920,7 +17920,7 @@
       <c r="A604" t="n">
         <v>603</v>
       </c>
-      <c r="B604" s="1" t="n">
+      <c r="B604" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C604" t="inlineStr">
@@ -17949,7 +17949,7 @@
       <c r="A605" t="n">
         <v>604</v>
       </c>
-      <c r="B605" s="1" t="n">
+      <c r="B605" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C605" t="inlineStr">
@@ -17978,7 +17978,7 @@
       <c r="A606" t="n">
         <v>605</v>
       </c>
-      <c r="B606" s="1" t="n">
+      <c r="B606" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C606" t="inlineStr">
@@ -18007,7 +18007,7 @@
       <c r="A607" t="n">
         <v>606</v>
       </c>
-      <c r="B607" s="1" t="n">
+      <c r="B607" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C607" t="inlineStr">
@@ -18036,7 +18036,7 @@
       <c r="A608" t="n">
         <v>607</v>
       </c>
-      <c r="B608" s="1" t="n">
+      <c r="B608" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C608" t="inlineStr">
@@ -18065,7 +18065,7 @@
       <c r="A609" t="n">
         <v>608</v>
       </c>
-      <c r="B609" s="1" t="n">
+      <c r="B609" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C609" t="inlineStr">
@@ -18094,7 +18094,7 @@
       <c r="A610" t="n">
         <v>609</v>
       </c>
-      <c r="B610" s="1" t="n">
+      <c r="B610" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C610" t="inlineStr">
@@ -18123,7 +18123,7 @@
       <c r="A611" t="n">
         <v>610</v>
       </c>
-      <c r="B611" s="1" t="n">
+      <c r="B611" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C611" t="inlineStr">
@@ -18152,7 +18152,7 @@
       <c r="A612" t="n">
         <v>611</v>
       </c>
-      <c r="B612" s="1" t="n">
+      <c r="B612" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C612" t="inlineStr">
@@ -18181,7 +18181,7 @@
       <c r="A613" t="n">
         <v>612</v>
       </c>
-      <c r="B613" s="1" t="n">
+      <c r="B613" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C613" t="inlineStr">
@@ -18210,7 +18210,7 @@
       <c r="A614" t="n">
         <v>613</v>
       </c>
-      <c r="B614" s="1" t="n">
+      <c r="B614" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C614" t="inlineStr">
@@ -18239,7 +18239,7 @@
       <c r="A615" t="n">
         <v>614</v>
       </c>
-      <c r="B615" s="1" t="n">
+      <c r="B615" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C615" t="inlineStr">
@@ -18268,7 +18268,7 @@
       <c r="A616" t="n">
         <v>615</v>
       </c>
-      <c r="B616" s="1" t="n">
+      <c r="B616" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C616" t="inlineStr">
@@ -18297,7 +18297,7 @@
       <c r="A617" t="n">
         <v>616</v>
       </c>
-      <c r="B617" s="1" t="n">
+      <c r="B617" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C617" t="inlineStr">
@@ -18326,7 +18326,7 @@
       <c r="A618" t="n">
         <v>617</v>
       </c>
-      <c r="B618" s="1" t="n">
+      <c r="B618" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C618" t="inlineStr">
@@ -18355,7 +18355,7 @@
       <c r="A619" t="n">
         <v>618</v>
       </c>
-      <c r="B619" s="1" t="n">
+      <c r="B619" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C619" t="inlineStr">
@@ -18384,7 +18384,7 @@
       <c r="A620" t="n">
         <v>619</v>
       </c>
-      <c r="B620" s="1" t="n">
+      <c r="B620" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C620" t="inlineStr">
@@ -18413,7 +18413,7 @@
       <c r="A621" t="n">
         <v>620</v>
       </c>
-      <c r="B621" s="1" t="n">
+      <c r="B621" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C621" t="inlineStr">
@@ -18442,7 +18442,7 @@
       <c r="A622" t="n">
         <v>621</v>
       </c>
-      <c r="B622" s="1" t="n">
+      <c r="B622" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C622" t="inlineStr">
@@ -18471,7 +18471,7 @@
       <c r="A623" t="n">
         <v>622</v>
       </c>
-      <c r="B623" s="1" t="n">
+      <c r="B623" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C623" t="inlineStr">
@@ -18500,7 +18500,7 @@
       <c r="A624" t="n">
         <v>623</v>
       </c>
-      <c r="B624" s="1" t="n">
+      <c r="B624" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C624" t="inlineStr">
@@ -18529,7 +18529,7 @@
       <c r="A625" t="n">
         <v>624</v>
       </c>
-      <c r="B625" s="1" t="n">
+      <c r="B625" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C625" t="inlineStr">
@@ -18558,7 +18558,7 @@
       <c r="A626" t="n">
         <v>625</v>
       </c>
-      <c r="B626" s="1" t="n">
+      <c r="B626" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C626" t="inlineStr">
@@ -18587,7 +18587,7 @@
       <c r="A627" t="n">
         <v>626</v>
       </c>
-      <c r="B627" s="1" t="n">
+      <c r="B627" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C627" t="inlineStr">
@@ -18616,7 +18616,7 @@
       <c r="A628" t="n">
         <v>627</v>
       </c>
-      <c r="B628" s="1" t="n">
+      <c r="B628" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C628" t="inlineStr">
@@ -18645,7 +18645,7 @@
       <c r="A629" t="n">
         <v>628</v>
       </c>
-      <c r="B629" s="1" t="n">
+      <c r="B629" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C629" t="inlineStr">
@@ -18674,7 +18674,7 @@
       <c r="A630" t="n">
         <v>629</v>
       </c>
-      <c r="B630" s="1" t="n">
+      <c r="B630" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C630" t="inlineStr">
@@ -18703,7 +18703,7 @@
       <c r="A631" t="n">
         <v>630</v>
       </c>
-      <c r="B631" s="1" t="n">
+      <c r="B631" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C631" t="inlineStr">
@@ -18732,7 +18732,7 @@
       <c r="A632" t="n">
         <v>631</v>
       </c>
-      <c r="B632" s="1" t="n">
+      <c r="B632" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C632" t="inlineStr">
@@ -18761,7 +18761,7 @@
       <c r="A633" t="n">
         <v>632</v>
       </c>
-      <c r="B633" s="1" t="n">
+      <c r="B633" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C633" t="inlineStr">
@@ -18790,7 +18790,7 @@
       <c r="A634" t="n">
         <v>633</v>
       </c>
-      <c r="B634" s="1" t="n">
+      <c r="B634" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C634" t="inlineStr">
@@ -18819,7 +18819,7 @@
       <c r="A635" t="n">
         <v>634</v>
       </c>
-      <c r="B635" s="1" t="n">
+      <c r="B635" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C635" t="inlineStr">
@@ -18848,7 +18848,7 @@
       <c r="A636" t="n">
         <v>635</v>
       </c>
-      <c r="B636" s="1" t="n">
+      <c r="B636" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C636" t="inlineStr">
@@ -18877,7 +18877,7 @@
       <c r="A637" t="n">
         <v>636</v>
       </c>
-      <c r="B637" s="1" t="n">
+      <c r="B637" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C637" t="inlineStr">
@@ -18906,7 +18906,7 @@
       <c r="A638" t="n">
         <v>637</v>
       </c>
-      <c r="B638" s="1" t="n">
+      <c r="B638" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C638" t="inlineStr">
@@ -18935,7 +18935,7 @@
       <c r="A639" t="n">
         <v>638</v>
       </c>
-      <c r="B639" s="1" t="n">
+      <c r="B639" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C639" t="inlineStr">
@@ -18964,7 +18964,7 @@
       <c r="A640" t="n">
         <v>639</v>
       </c>
-      <c r="B640" s="1" t="n">
+      <c r="B640" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C640" t="inlineStr">
@@ -18993,7 +18993,7 @@
       <c r="A641" t="n">
         <v>640</v>
       </c>
-      <c r="B641" s="1" t="n">
+      <c r="B641" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C641" t="inlineStr">
@@ -19022,7 +19022,7 @@
       <c r="A642" t="n">
         <v>641</v>
       </c>
-      <c r="B642" s="1" t="n">
+      <c r="B642" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C642" t="inlineStr">
@@ -19051,7 +19051,7 @@
       <c r="A643" t="n">
         <v>642</v>
       </c>
-      <c r="B643" s="1" t="n">
+      <c r="B643" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C643" t="inlineStr">
@@ -19080,7 +19080,7 @@
       <c r="A644" t="n">
         <v>643</v>
       </c>
-      <c r="B644" s="1" t="n">
+      <c r="B644" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C644" t="inlineStr">
@@ -19109,7 +19109,7 @@
       <c r="A645" t="n">
         <v>644</v>
       </c>
-      <c r="B645" s="1" t="n">
+      <c r="B645" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C645" t="inlineStr">
@@ -19138,7 +19138,7 @@
       <c r="A646" t="n">
         <v>645</v>
       </c>
-      <c r="B646" s="1" t="n">
+      <c r="B646" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C646" t="inlineStr">
@@ -19167,7 +19167,7 @@
       <c r="A647" t="n">
         <v>646</v>
       </c>
-      <c r="B647" s="1" t="n">
+      <c r="B647" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C647" t="inlineStr">
@@ -19196,7 +19196,7 @@
       <c r="A648" t="n">
         <v>647</v>
       </c>
-      <c r="B648" s="1" t="n">
+      <c r="B648" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C648" t="inlineStr">
@@ -19225,7 +19225,7 @@
       <c r="A649" t="n">
         <v>648</v>
       </c>
-      <c r="B649" s="1" t="n">
+      <c r="B649" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C649" t="inlineStr">
@@ -19254,7 +19254,7 @@
       <c r="A650" t="n">
         <v>649</v>
       </c>
-      <c r="B650" s="1" t="n">
+      <c r="B650" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C650" t="inlineStr">
@@ -19283,7 +19283,7 @@
       <c r="A651" t="n">
         <v>650</v>
       </c>
-      <c r="B651" s="1" t="n">
+      <c r="B651" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C651" t="inlineStr">
@@ -19312,7 +19312,7 @@
       <c r="A652" t="n">
         <v>651</v>
       </c>
-      <c r="B652" s="1" t="n">
+      <c r="B652" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C652" t="inlineStr">
@@ -19341,7 +19341,7 @@
       <c r="A653" t="n">
         <v>652</v>
       </c>
-      <c r="B653" s="1" t="n">
+      <c r="B653" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C653" t="inlineStr">
@@ -19370,7 +19370,7 @@
       <c r="A654" t="n">
         <v>653</v>
       </c>
-      <c r="B654" s="1" t="n">
+      <c r="B654" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C654" t="inlineStr">
@@ -19399,7 +19399,7 @@
       <c r="A655" t="n">
         <v>654</v>
       </c>
-      <c r="B655" s="1" t="n">
+      <c r="B655" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C655" t="inlineStr">
@@ -19428,7 +19428,7 @@
       <c r="A656" t="n">
         <v>655</v>
       </c>
-      <c r="B656" s="1" t="n">
+      <c r="B656" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C656" t="inlineStr">
@@ -19457,7 +19457,7 @@
       <c r="A657" t="n">
         <v>656</v>
       </c>
-      <c r="B657" s="1" t="n">
+      <c r="B657" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C657" t="inlineStr">
@@ -19486,7 +19486,7 @@
       <c r="A658" t="n">
         <v>657</v>
       </c>
-      <c r="B658" s="1" t="n">
+      <c r="B658" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C658" t="inlineStr">
@@ -19515,7 +19515,7 @@
       <c r="A659" t="n">
         <v>658</v>
       </c>
-      <c r="B659" s="1" t="n">
+      <c r="B659" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C659" t="inlineStr">
@@ -19544,7 +19544,7 @@
       <c r="A660" t="n">
         <v>659</v>
       </c>
-      <c r="B660" s="1" t="n">
+      <c r="B660" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C660" t="inlineStr">
@@ -19573,7 +19573,7 @@
       <c r="A661" t="n">
         <v>660</v>
       </c>
-      <c r="B661" s="1" t="n">
+      <c r="B661" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C661" t="inlineStr">
@@ -19602,7 +19602,7 @@
       <c r="A662" t="n">
         <v>661</v>
       </c>
-      <c r="B662" s="1" t="n">
+      <c r="B662" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C662" t="inlineStr">
@@ -19631,7 +19631,7 @@
       <c r="A663" t="n">
         <v>662</v>
       </c>
-      <c r="B663" s="1" t="n">
+      <c r="B663" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C663" t="inlineStr">
@@ -19660,7 +19660,7 @@
       <c r="A664" t="n">
         <v>663</v>
       </c>
-      <c r="B664" s="1" t="n">
+      <c r="B664" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C664" t="inlineStr">
@@ -19689,7 +19689,7 @@
       <c r="A665" t="n">
         <v>664</v>
       </c>
-      <c r="B665" s="1" t="n">
+      <c r="B665" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="C665" t="inlineStr">
@@ -19718,7 +19718,7 @@
       <c r="A666" t="n">
         <v>665</v>
       </c>
-      <c r="B666" s="1" t="n">
+      <c r="B666" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C666" t="inlineStr">
@@ -19747,7 +19747,7 @@
       <c r="A667" t="n">
         <v>666</v>
       </c>
-      <c r="B667" s="1" t="n">
+      <c r="B667" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C667" t="inlineStr">
@@ -19776,7 +19776,7 @@
       <c r="A668" t="n">
         <v>667</v>
       </c>
-      <c r="B668" s="1" t="n">
+      <c r="B668" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C668" t="inlineStr">
@@ -19805,7 +19805,7 @@
       <c r="A669" t="n">
         <v>668</v>
       </c>
-      <c r="B669" s="1" t="n">
+      <c r="B669" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C669" t="inlineStr">
@@ -19834,7 +19834,7 @@
       <c r="A670" t="n">
         <v>669</v>
       </c>
-      <c r="B670" s="1" t="n">
+      <c r="B670" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C670" t="inlineStr">
@@ -19863,7 +19863,7 @@
       <c r="A671" t="n">
         <v>670</v>
       </c>
-      <c r="B671" s="1" t="n">
+      <c r="B671" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C671" t="inlineStr">
@@ -19892,7 +19892,7 @@
       <c r="A672" t="n">
         <v>671</v>
       </c>
-      <c r="B672" s="1" t="n">
+      <c r="B672" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C672" t="inlineStr">
@@ -19921,7 +19921,7 @@
       <c r="A673" t="n">
         <v>672</v>
       </c>
-      <c r="B673" s="1" t="n">
+      <c r="B673" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C673" t="inlineStr">
@@ -19950,7 +19950,7 @@
       <c r="A674" t="n">
         <v>673</v>
       </c>
-      <c r="B674" s="1" t="n">
+      <c r="B674" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C674" t="inlineStr">
@@ -19979,7 +19979,7 @@
       <c r="A675" t="n">
         <v>674</v>
       </c>
-      <c r="B675" s="1" t="n">
+      <c r="B675" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C675" t="inlineStr">
@@ -20008,7 +20008,7 @@
       <c r="A676" t="n">
         <v>675</v>
       </c>
-      <c r="B676" s="1" t="n">
+      <c r="B676" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C676" t="inlineStr">
@@ -20037,7 +20037,7 @@
       <c r="A677" t="n">
         <v>676</v>
       </c>
-      <c r="B677" s="1" t="n">
+      <c r="B677" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C677" t="inlineStr">
@@ -20066,7 +20066,7 @@
       <c r="A678" t="n">
         <v>677</v>
       </c>
-      <c r="B678" s="1" t="n">
+      <c r="B678" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C678" t="inlineStr">
@@ -20095,7 +20095,7 @@
       <c r="A679" t="n">
         <v>678</v>
       </c>
-      <c r="B679" s="1" t="n">
+      <c r="B679" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="C679" t="inlineStr">
@@ -20124,7 +20124,7 @@
       <c r="A680" t="n">
         <v>679</v>
       </c>
-      <c r="B680" s="1" t="n">
+      <c r="B680" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="C680" t="inlineStr">
@@ -20153,7 +20153,7 @@
       <c r="A681" t="n">
         <v>680</v>
       </c>
-      <c r="B681" s="1" t="n">
+      <c r="B681" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="C681" t="inlineStr">
@@ -20182,7 +20182,7 @@
       <c r="A682" t="n">
         <v>681</v>
       </c>
-      <c r="B682" s="1" t="n">
+      <c r="B682" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="C682" t="inlineStr">
@@ -20211,7 +20211,7 @@
       <c r="A683" t="n">
         <v>682</v>
       </c>
-      <c r="B683" s="1" t="n">
+      <c r="B683" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="C683" t="inlineStr">
@@ -20270,7 +20270,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>802,743.79</t>
+          <t>802,743.90</t>
         </is>
       </c>
     </row>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9,284,442.92</t>
+          <t>9,284,442.94</t>
         </is>
       </c>
     </row>
@@ -20294,7 +20294,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10,087,186.71</t>
+          <t>10,087,186.84</t>
         </is>
       </c>
     </row>

--- a/outputs/Arac_Planlama.xlsx
+++ b/outputs/Arac_Planlama.xlsx
@@ -17,10 +17,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -50,9 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -454,8 +450,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46153</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -480,8 +478,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>46154</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -506,8 +506,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>46155</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -532,8 +534,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>46156</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -558,8 +562,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>46157</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -584,8 +590,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>46158</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -610,8 +618,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>46153</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -636,8 +646,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>46154</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -662,8 +674,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>46155</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -688,8 +702,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>46156</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -714,8 +730,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>46157</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -740,8 +758,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>46158</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -766,8 +786,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>46153</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -792,8 +814,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>46154</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -818,8 +842,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>46155</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -844,8 +870,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>46156</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -870,8 +898,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>46157</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -896,8 +926,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>46158</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -922,8 +954,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>46153</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -948,8 +982,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>46154</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -974,8 +1010,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>46155</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1000,8 +1038,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>46156</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1026,8 +1066,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>46157</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1052,8 +1094,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>46158</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1078,8 +1122,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>46153</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1104,8 +1150,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>46154</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1130,8 +1178,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>46155</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1156,8 +1206,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>46156</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1182,8 +1234,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>46157</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1208,8 +1262,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>46158</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1234,8 +1290,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>46153</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1260,8 +1318,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>46154</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1286,8 +1346,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>46155</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1312,8 +1374,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>46156</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1338,8 +1402,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>46157</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1364,8 +1430,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>46158</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1390,8 +1458,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>46153</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1416,8 +1486,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>46154</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1442,8 +1514,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>46155</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1468,8 +1542,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>46156</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1494,8 +1570,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>46157</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1520,8 +1598,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>46158</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1546,8 +1626,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>46153</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1572,8 +1654,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>46154</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1598,8 +1682,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>46155</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1624,8 +1710,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>46156</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1650,8 +1738,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>46157</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1676,8 +1766,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>46158</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1702,8 +1794,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>46153</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -1728,8 +1822,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>46154</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -1754,8 +1850,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>46155</v>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -1780,8 +1878,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>46156</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -1806,8 +1906,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>46157</v>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -1832,8 +1934,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>46158</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -1858,8 +1962,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>46159</v>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -1884,8 +1990,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
-        <v>46153</v>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -1910,8 +2018,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
-        <v>46154</v>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -1936,8 +2046,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>46155</v>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -1962,8 +2074,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>46156</v>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -1988,8 +2102,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
-        <v>46157</v>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2014,8 +2130,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
-        <v>46158</v>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2040,8 +2158,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
-        <v>46153</v>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2066,8 +2186,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
-        <v>46154</v>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2092,8 +2214,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
-        <v>46155</v>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2118,8 +2242,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
-        <v>46156</v>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -2144,8 +2270,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
-        <v>46157</v>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2170,8 +2298,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
-        <v>46158</v>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -2196,8 +2326,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
-        <v>46153</v>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -2222,8 +2354,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
-        <v>46154</v>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -2248,8 +2382,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
-        <v>46155</v>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -2274,8 +2410,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
-        <v>46156</v>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -2300,8 +2438,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
-        <v>46157</v>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -2326,8 +2466,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
-        <v>46158</v>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -2352,8 +2494,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
-        <v>46153</v>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -2378,8 +2522,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
-        <v>46154</v>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -2404,8 +2550,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
-        <v>46155</v>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -2430,8 +2578,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
-        <v>46156</v>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -2456,8 +2606,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
-        <v>46157</v>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -2482,8 +2634,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
-        <v>46158</v>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -2508,8 +2662,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
-        <v>46153</v>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -2534,8 +2690,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
-        <v>46154</v>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -2560,8 +2718,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
-        <v>46155</v>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -2586,8 +2746,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
-        <v>46156</v>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -2612,8 +2774,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
-        <v>46157</v>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -2638,8 +2802,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
-        <v>46158</v>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -2664,8 +2830,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
-        <v>46159</v>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -2690,8 +2858,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
-        <v>46153</v>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -2716,8 +2886,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
-        <v>46154</v>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -2742,8 +2914,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
-        <v>46155</v>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -2768,8 +2942,10 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
-        <v>46156</v>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -2794,8 +2970,10 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
-        <v>46157</v>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -2820,8 +2998,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
-        <v>46158</v>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -2846,8 +3026,10 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
-        <v>46153</v>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -2872,8 +3054,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
-        <v>46154</v>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -2898,8 +3082,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
-        <v>46155</v>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -2924,8 +3110,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
-        <v>46156</v>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -2950,8 +3138,10 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
-        <v>46157</v>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -2976,8 +3166,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
-        <v>46158</v>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -3002,8 +3194,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
-        <v>46153</v>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -3028,8 +3222,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
-        <v>46154</v>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -3054,8 +3250,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
-        <v>46155</v>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -3080,8 +3278,10 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
-        <v>46156</v>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -3106,8 +3306,10 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
-        <v>46157</v>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -3132,8 +3334,10 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
-        <v>46158</v>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -3158,8 +3362,10 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
-        <v>46159</v>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -3184,8 +3390,10 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
-        <v>46153</v>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -3210,8 +3418,10 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
-        <v>46153</v>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -3236,8 +3446,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
-        <v>46154</v>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -3262,8 +3474,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
-        <v>46155</v>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -3288,8 +3502,10 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
-        <v>46156</v>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -3314,8 +3530,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
-        <v>46157</v>
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -3340,8 +3558,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
-        <v>46158</v>
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -3366,8 +3586,10 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
-        <v>46159</v>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -3392,8 +3614,10 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
-        <v>46153</v>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -3418,8 +3642,10 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
-        <v>46154</v>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -3444,8 +3670,10 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
-        <v>46155</v>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -3470,8 +3698,10 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
-        <v>46156</v>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -3496,8 +3726,10 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
-        <v>46157</v>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -3522,8 +3754,10 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
-        <v>46158</v>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -3548,8 +3782,10 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
-        <v>46159</v>
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -3574,8 +3810,10 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
-        <v>46153</v>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -3600,8 +3838,10 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
-        <v>46154</v>
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -3626,8 +3866,10 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
-        <v>46155</v>
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -3652,8 +3894,10 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
-        <v>46156</v>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -3678,8 +3922,10 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
-        <v>46157</v>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -3704,8 +3950,10 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
-        <v>46158</v>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -3730,8 +3978,10 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
-        <v>46153</v>
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -3756,8 +4006,10 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
-        <v>46153</v>
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -3782,8 +4034,10 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
-        <v>46154</v>
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -3808,8 +4062,10 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
-        <v>46154</v>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -3834,8 +4090,10 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
-        <v>46155</v>
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -3860,8 +4118,10 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
-        <v>46155</v>
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -3886,8 +4146,10 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
-        <v>46156</v>
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -3912,8 +4174,10 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
-        <v>46156</v>
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -3938,8 +4202,10 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
-        <v>46157</v>
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -3964,8 +4230,10 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
-        <v>46157</v>
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -3990,8 +4258,10 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
-        <v>46158</v>
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -4016,8 +4286,10 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
-        <v>46158</v>
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -4042,8 +4314,10 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
-        <v>46159</v>
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -4068,8 +4342,10 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
-        <v>46159</v>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -4094,8 +4370,10 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
-        <v>46153</v>
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -4120,8 +4398,10 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
-        <v>46154</v>
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -4146,8 +4426,10 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
-        <v>46155</v>
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -4172,8 +4454,10 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
-        <v>46156</v>
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -4198,8 +4482,10 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
-        <v>46157</v>
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -4224,8 +4510,10 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
-        <v>46158</v>
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -4250,8 +4538,10 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
-        <v>46159</v>
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -4276,8 +4566,10 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
-        <v>46153</v>
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -4302,8 +4594,10 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
-        <v>46154</v>
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -4328,8 +4622,10 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
-        <v>46155</v>
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -4354,8 +4650,10 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
-        <v>46156</v>
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -4380,8 +4678,10 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
-        <v>46157</v>
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -4406,8 +4706,10 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
-        <v>46158</v>
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -4432,8 +4734,10 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
-        <v>46159</v>
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -4458,8 +4762,10 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
-        <v>46153</v>
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -4484,8 +4790,10 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
-        <v>46153</v>
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -4510,8 +4818,10 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
-        <v>46154</v>
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -4536,8 +4846,10 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
-        <v>46154</v>
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -4562,8 +4874,10 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
-        <v>46155</v>
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -4588,8 +4902,10 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
-        <v>46155</v>
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -4614,8 +4930,10 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
-        <v>46156</v>
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -4640,8 +4958,10 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
-        <v>46156</v>
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -4666,8 +4986,10 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
-        <v>46157</v>
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -4692,8 +5014,10 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
-        <v>46157</v>
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -4718,8 +5042,10 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
-        <v>46158</v>
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -4744,8 +5070,10 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
-        <v>46158</v>
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -4770,8 +5098,10 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
-        <v>46159</v>
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -4796,8 +5126,10 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
-        <v>46159</v>
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -4822,8 +5154,10 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
-        <v>46153</v>
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -4848,8 +5182,10 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
-        <v>46154</v>
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -4874,8 +5210,10 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
-        <v>46155</v>
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -4900,8 +5238,10 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
-        <v>46156</v>
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -4926,8 +5266,10 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
-        <v>46157</v>
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -4952,8 +5294,10 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
-        <v>46158</v>
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -4978,8 +5322,10 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
-        <v>46159</v>
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -5004,8 +5350,10 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
-        <v>46153</v>
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -5030,8 +5378,10 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
-        <v>46154</v>
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -5056,8 +5406,10 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
-        <v>46155</v>
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -5082,8 +5434,10 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
-        <v>46156</v>
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -5108,8 +5462,10 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
-        <v>46157</v>
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -5134,8 +5490,10 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
-        <v>46158</v>
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -5160,8 +5518,10 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
-        <v>46159</v>
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -5186,8 +5546,10 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
-        <v>46153</v>
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -5212,8 +5574,10 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
-        <v>46154</v>
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -5238,8 +5602,10 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
-        <v>46155</v>
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -5264,8 +5630,10 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
-        <v>46156</v>
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -5290,8 +5658,10 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
-        <v>46157</v>
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -5316,8 +5686,10 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
-        <v>46158</v>
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -5342,8 +5714,10 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
-        <v>46159</v>
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -5368,8 +5742,10 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
-        <v>46153</v>
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -5394,8 +5770,10 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
-        <v>46154</v>
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -5420,8 +5798,10 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
-        <v>46155</v>
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -5446,8 +5826,10 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
-        <v>46156</v>
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -5472,8 +5854,10 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
-        <v>46157</v>
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -5498,8 +5882,10 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
-        <v>46158</v>
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -5524,8 +5910,10 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
-        <v>46159</v>
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -5550,8 +5938,10 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
-        <v>46153</v>
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -5576,8 +5966,10 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
-        <v>46154</v>
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -5602,8 +5994,10 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
-        <v>46155</v>
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -5628,8 +6022,10 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
-        <v>46156</v>
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -5654,8 +6050,10 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
-        <v>46157</v>
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -5680,8 +6078,10 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
-        <v>46158</v>
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -5706,8 +6106,10 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
-        <v>46159</v>
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -5732,8 +6134,10 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
-        <v>46153</v>
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -5758,8 +6162,10 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
-        <v>46154</v>
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -5784,8 +6190,10 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
-        <v>46155</v>
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -5810,8 +6218,10 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
-        <v>46156</v>
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -5836,8 +6246,10 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
-        <v>46157</v>
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -5862,8 +6274,10 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
-        <v>46158</v>
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -5888,8 +6302,10 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
-        <v>46159</v>
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -5914,8 +6330,10 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
-        <v>46153</v>
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -5940,8 +6358,10 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
-        <v>46153</v>
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -5966,8 +6386,10 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
-        <v>46154</v>
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -5992,8 +6414,10 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
-        <v>46154</v>
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -6018,8 +6442,10 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
-        <v>46155</v>
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -6044,8 +6470,10 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
-        <v>46155</v>
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -6070,8 +6498,10 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
-        <v>46156</v>
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -6096,8 +6526,10 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
-        <v>46157</v>
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -6122,8 +6554,10 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
-        <v>46158</v>
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -6148,8 +6582,10 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
-        <v>46159</v>
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -6174,8 +6610,10 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
-        <v>46153</v>
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -6200,8 +6638,10 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
-        <v>46153</v>
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -6226,8 +6666,10 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
-        <v>46154</v>
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -6252,8 +6694,10 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
-        <v>46154</v>
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -6278,8 +6722,10 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
-        <v>46155</v>
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -6304,8 +6750,10 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
-        <v>46155</v>
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -6330,8 +6778,10 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
-        <v>46156</v>
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -6356,8 +6806,10 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
-        <v>46156</v>
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -6382,8 +6834,10 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
-        <v>46157</v>
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -6408,8 +6862,10 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
-        <v>46157</v>
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -6434,8 +6890,10 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
-        <v>46158</v>
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -6460,8 +6918,10 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
-        <v>46159</v>
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -6486,8 +6946,10 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
-        <v>46153</v>
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -6512,8 +6974,10 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
-        <v>46153</v>
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -6538,8 +7002,10 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
-        <v>46154</v>
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -6564,8 +7030,10 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
-        <v>46154</v>
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -6590,8 +7058,10 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
-        <v>46155</v>
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -6616,8 +7086,10 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
-        <v>46155</v>
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
@@ -6642,8 +7114,10 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
-        <v>46156</v>
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -6668,8 +7142,10 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
-        <v>46157</v>
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
@@ -6694,8 +7170,10 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
-        <v>46158</v>
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
@@ -6720,8 +7198,10 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
-        <v>46159</v>
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -6746,8 +7226,10 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
-        <v>46153</v>
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
@@ -6772,8 +7254,10 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
-        <v>46154</v>
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
@@ -6798,8 +7282,10 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
-        <v>46155</v>
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -6824,8 +7310,10 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
-        <v>46156</v>
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
@@ -6850,8 +7338,10 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
-        <v>46157</v>
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -6876,8 +7366,10 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
-        <v>46158</v>
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
@@ -6902,8 +7394,10 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
-        <v>46159</v>
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -6928,8 +7422,10 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
-        <v>46153</v>
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
@@ -6954,8 +7450,10 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
-        <v>46154</v>
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
@@ -6980,8 +7478,10 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
-        <v>46155</v>
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
@@ -7006,8 +7506,10 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
-        <v>46156</v>
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
@@ -7032,8 +7534,10 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
-        <v>46157</v>
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
@@ -7058,8 +7562,10 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
-        <v>46158</v>
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
@@ -7084,8 +7590,10 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
-        <v>46153</v>
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
@@ -7110,8 +7618,10 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
-        <v>46153</v>
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
@@ -7136,8 +7646,10 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
-        <v>46154</v>
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
@@ -7162,8 +7674,10 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
-        <v>46155</v>
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
@@ -7188,8 +7702,10 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
-        <v>46156</v>
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
@@ -7214,8 +7730,10 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
-        <v>46157</v>
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
@@ -7240,8 +7758,10 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
-        <v>46158</v>
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
@@ -7266,8 +7786,10 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
-        <v>46159</v>
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -7292,8 +7814,10 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
-        <v>46153</v>
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
@@ -7318,8 +7842,10 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
-        <v>46154</v>
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
@@ -7344,8 +7870,10 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
-        <v>46155</v>
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
@@ -7370,8 +7898,10 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
-        <v>46156</v>
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
@@ -7396,8 +7926,10 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
-        <v>46157</v>
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
@@ -7422,8 +7954,10 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
-        <v>46158</v>
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
@@ -7448,8 +7982,10 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
-        <v>46159</v>
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
@@ -7474,8 +8010,10 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
-        <v>46153</v>
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
@@ -7500,8 +8038,10 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
-        <v>46154</v>
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
@@ -7526,8 +8066,10 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
-        <v>46155</v>
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
@@ -7552,8 +8094,10 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
-        <v>46156</v>
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
@@ -7578,8 +8122,10 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
-        <v>46157</v>
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
@@ -7604,8 +8150,10 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
-        <v>46158</v>
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
@@ -7630,8 +8178,10 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
-        <v>46159</v>
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
@@ -7656,8 +8206,10 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
-        <v>46153</v>
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
@@ -7682,8 +8234,10 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
-        <v>46153</v>
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
@@ -7708,8 +8262,10 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
-        <v>46154</v>
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
@@ -7734,8 +8290,10 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
-        <v>46155</v>
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
@@ -7760,8 +8318,10 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
-        <v>46156</v>
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
@@ -7786,8 +8346,10 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
-        <v>46157</v>
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
@@ -7812,8 +8374,10 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
-        <v>46158</v>
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
@@ -7838,8 +8402,10 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
-        <v>46159</v>
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
@@ -7864,8 +8430,10 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
-        <v>46153</v>
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
@@ -7890,8 +8458,10 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
-        <v>46154</v>
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
@@ -7916,8 +8486,10 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
-        <v>46155</v>
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
@@ -7942,8 +8514,10 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
-        <v>46156</v>
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
@@ -7968,8 +8542,10 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
-        <v>46157</v>
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
@@ -7994,8 +8570,10 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
-        <v>46158</v>
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
@@ -8020,8 +8598,10 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
-        <v>46159</v>
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
@@ -8046,8 +8626,10 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
-        <v>46153</v>
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
@@ -8072,8 +8654,10 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
-        <v>46154</v>
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
@@ -8098,8 +8682,10 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
-        <v>46155</v>
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
@@ -8124,8 +8710,10 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
-        <v>46156</v>
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
@@ -8150,8 +8738,10 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
-        <v>46157</v>
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
@@ -8176,8 +8766,10 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
-        <v>46158</v>
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
@@ -8202,8 +8794,10 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
-        <v>46159</v>
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
@@ -8228,8 +8822,10 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
-        <v>46153</v>
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
@@ -8254,8 +8850,10 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
-        <v>46154</v>
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
@@ -8280,8 +8878,10 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
-        <v>46155</v>
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
@@ -8306,8 +8906,10 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
-        <v>46156</v>
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
@@ -8332,8 +8934,10 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
-        <v>46157</v>
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
@@ -8358,8 +8962,10 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
-        <v>46158</v>
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
@@ -8384,8 +8990,10 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
-        <v>46159</v>
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
@@ -8410,8 +9018,10 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
-        <v>46153</v>
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
@@ -8436,8 +9046,10 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
-        <v>46154</v>
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
@@ -8462,8 +9074,10 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
-        <v>46155</v>
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
@@ -8488,8 +9102,10 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
-        <v>46156</v>
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
@@ -8514,8 +9130,10 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
-        <v>46157</v>
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
@@ -8540,8 +9158,10 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
-        <v>46158</v>
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
@@ -8566,8 +9186,10 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
-        <v>46159</v>
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
@@ -8592,8 +9214,10 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="n">
-        <v>46153</v>
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
@@ -8618,8 +9242,10 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="n">
-        <v>46153</v>
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
@@ -8644,8 +9270,10 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="n">
-        <v>46154</v>
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
@@ -8670,8 +9298,10 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="n">
-        <v>46155</v>
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
@@ -8696,8 +9326,10 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="1" t="n">
-        <v>46156</v>
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
@@ -8722,8 +9354,10 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="1" t="n">
-        <v>46157</v>
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
@@ -8748,8 +9382,10 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="1" t="n">
-        <v>46158</v>
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
@@ -8774,8 +9410,10 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="1" t="n">
-        <v>46159</v>
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
@@ -8800,8 +9438,10 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="1" t="n">
-        <v>46153</v>
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
@@ -8826,8 +9466,10 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="1" t="n">
-        <v>46153</v>
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
@@ -8852,8 +9494,10 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="1" t="n">
-        <v>46154</v>
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
@@ -8878,8 +9522,10 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="1" t="n">
-        <v>46155</v>
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
@@ -8904,8 +9550,10 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="1" t="n">
-        <v>46156</v>
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
@@ -8930,8 +9578,10 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="1" t="n">
-        <v>46157</v>
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
@@ -8956,8 +9606,10 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="1" t="n">
-        <v>46158</v>
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
@@ -8982,8 +9634,10 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="1" t="n">
-        <v>46159</v>
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
@@ -9008,8 +9662,10 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="1" t="n">
-        <v>46153</v>
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
@@ -9034,8 +9690,10 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="1" t="n">
-        <v>46153</v>
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
@@ -9060,8 +9718,10 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="1" t="n">
-        <v>46154</v>
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
@@ -9086,8 +9746,10 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="1" t="n">
-        <v>46155</v>
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
@@ -9112,8 +9774,10 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="1" t="n">
-        <v>46156</v>
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
@@ -9138,8 +9802,10 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="1" t="n">
-        <v>46157</v>
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
@@ -9164,8 +9830,10 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="1" t="n">
-        <v>46158</v>
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
@@ -9190,8 +9858,10 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="1" t="n">
-        <v>46159</v>
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
@@ -9216,8 +9886,10 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="1" t="n">
-        <v>46153</v>
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
@@ -9242,8 +9914,10 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="1" t="n">
-        <v>46154</v>
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
@@ -9268,8 +9942,10 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="1" t="n">
-        <v>46155</v>
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
@@ -9294,8 +9970,10 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="1" t="n">
-        <v>46156</v>
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
@@ -9320,8 +9998,10 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="1" t="n">
-        <v>46157</v>
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
@@ -9346,8 +10026,10 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="1" t="n">
-        <v>46158</v>
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
@@ -9372,8 +10054,10 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="1" t="n">
-        <v>46153</v>
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
@@ -9398,8 +10082,10 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="1" t="n">
-        <v>46154</v>
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
@@ -9424,8 +10110,10 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="1" t="n">
-        <v>46155</v>
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
@@ -9450,8 +10138,10 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="1" t="n">
-        <v>46156</v>
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
@@ -9476,8 +10166,10 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="1" t="n">
-        <v>46153</v>
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
@@ -9502,8 +10194,10 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="1" t="n">
-        <v>46154</v>
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
@@ -9528,8 +10222,10 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="1" t="n">
-        <v>46155</v>
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
@@ -9554,8 +10250,10 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="1" t="n">
-        <v>46156</v>
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
@@ -9580,8 +10278,10 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="1" t="n">
-        <v>46157</v>
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
@@ -9606,8 +10306,10 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="1" t="n">
-        <v>46158</v>
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
@@ -9632,8 +10334,10 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="1" t="n">
-        <v>46159</v>
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
@@ -9658,8 +10362,10 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="1" t="n">
-        <v>46153</v>
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
@@ -9684,8 +10390,10 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="1" t="n">
-        <v>46153</v>
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
@@ -9710,8 +10418,10 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="1" t="n">
-        <v>46154</v>
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
@@ -9736,8 +10446,10 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="1" t="n">
-        <v>46155</v>
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
@@ -9762,8 +10474,10 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="1" t="n">
-        <v>46156</v>
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
@@ -9788,8 +10502,10 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="1" t="n">
-        <v>46157</v>
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
@@ -9814,8 +10530,10 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="1" t="n">
-        <v>46158</v>
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
@@ -9840,8 +10558,10 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="1" t="n">
-        <v>46159</v>
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
@@ -9866,8 +10586,10 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="1" t="n">
-        <v>46153</v>
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
@@ -9892,8 +10614,10 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="1" t="n">
-        <v>46154</v>
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
@@ -9918,8 +10642,10 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="1" t="n">
-        <v>46155</v>
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
@@ -9944,8 +10670,10 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="1" t="n">
-        <v>46156</v>
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
@@ -9970,8 +10698,10 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="1" t="n">
-        <v>46157</v>
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
@@ -9996,8 +10726,10 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="1" t="n">
-        <v>46158</v>
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
@@ -10022,8 +10754,10 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="1" t="n">
-        <v>46153</v>
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
@@ -10048,8 +10782,10 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="1" t="n">
-        <v>46154</v>
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
@@ -10074,8 +10810,10 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="1" t="n">
-        <v>46155</v>
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
@@ -10100,8 +10838,10 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="1" t="n">
-        <v>46156</v>
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
@@ -10126,8 +10866,10 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="1" t="n">
-        <v>46157</v>
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
@@ -10152,8 +10894,10 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="1" t="n">
-        <v>46158</v>
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
@@ -10178,8 +10922,10 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="1" t="n">
-        <v>46153</v>
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
@@ -10204,8 +10950,10 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="1" t="n">
-        <v>46153</v>
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
@@ -10230,8 +10978,10 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="1" t="n">
-        <v>46154</v>
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
@@ -10256,8 +11006,10 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="1" t="n">
-        <v>46155</v>
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
@@ -10282,8 +11034,10 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="1" t="n">
-        <v>46156</v>
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
@@ -10308,8 +11062,10 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="1" t="n">
-        <v>46157</v>
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
@@ -10334,8 +11090,10 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="1" t="n">
-        <v>46158</v>
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
@@ -10360,8 +11118,10 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="1" t="n">
-        <v>46159</v>
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
@@ -10386,8 +11146,10 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="1" t="n">
-        <v>46153</v>
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
@@ -10412,8 +11174,10 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="1" t="n">
-        <v>46154</v>
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
@@ -10438,8 +11202,10 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="1" t="n">
-        <v>46155</v>
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
@@ -10464,8 +11230,10 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="1" t="n">
-        <v>46156</v>
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
@@ -10490,8 +11258,10 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="1" t="n">
-        <v>46157</v>
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
@@ -10516,8 +11286,10 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="1" t="n">
-        <v>46158</v>
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
@@ -10542,8 +11314,10 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="1" t="n">
-        <v>46153</v>
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
@@ -10568,8 +11342,10 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="1" t="n">
-        <v>46154</v>
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
@@ -10594,8 +11370,10 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="1" t="n">
-        <v>46155</v>
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
@@ -10620,8 +11398,10 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="1" t="n">
-        <v>46156</v>
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
@@ -10646,8 +11426,10 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="1" t="n">
-        <v>46157</v>
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
@@ -10672,8 +11454,10 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="1" t="n">
-        <v>46158</v>
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
@@ -10698,8 +11482,10 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="1" t="n">
-        <v>46153</v>
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
@@ -10724,8 +11510,10 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="1" t="n">
-        <v>46154</v>
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
@@ -10750,8 +11538,10 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="1" t="n">
-        <v>46155</v>
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
@@ -10776,8 +11566,10 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="1" t="n">
-        <v>46156</v>
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
@@ -10802,8 +11594,10 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="1" t="n">
-        <v>46157</v>
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
@@ -10828,8 +11622,10 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="1" t="n">
-        <v>46158</v>
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
@@ -10854,8 +11650,10 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="1" t="n">
-        <v>46153</v>
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
@@ -10880,8 +11678,10 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="1" t="n">
-        <v>46153</v>
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
@@ -10906,8 +11706,10 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="1" t="n">
-        <v>46154</v>
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
@@ -10932,8 +11734,10 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="1" t="n">
-        <v>46155</v>
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
@@ -10958,8 +11762,10 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="1" t="n">
-        <v>46156</v>
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
@@ -10984,8 +11790,10 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="1" t="n">
-        <v>46157</v>
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
@@ -11010,8 +11818,10 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="1" t="n">
-        <v>46158</v>
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
@@ -11036,8 +11846,10 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="1" t="n">
-        <v>46159</v>
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
@@ -11062,8 +11874,10 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="1" t="n">
-        <v>46153</v>
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
@@ -11088,8 +11902,10 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="1" t="n">
-        <v>46154</v>
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
@@ -11114,8 +11930,10 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="1" t="n">
-        <v>46155</v>
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
@@ -11140,8 +11958,10 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="1" t="n">
-        <v>46156</v>
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
@@ -11166,8 +11986,10 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="1" t="n">
-        <v>46157</v>
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
@@ -11192,8 +12014,10 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="1" t="n">
-        <v>46158</v>
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
@@ -11218,8 +12042,10 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="1" t="n">
-        <v>46153</v>
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
@@ -11244,8 +12070,10 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="1" t="n">
-        <v>46153</v>
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
@@ -11270,8 +12098,10 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="1" t="n">
-        <v>46154</v>
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
@@ -11296,8 +12126,10 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="1" t="n">
-        <v>46154</v>
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
@@ -11322,8 +12154,10 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="1" t="n">
-        <v>46155</v>
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
@@ -11348,8 +12182,10 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="1" t="n">
-        <v>46155</v>
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
@@ -11374,8 +12210,10 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="1" t="n">
-        <v>46156</v>
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
@@ -11400,8 +12238,10 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="1" t="n">
-        <v>46157</v>
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
@@ -11426,8 +12266,10 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="1" t="n">
-        <v>46158</v>
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
@@ -11452,8 +12294,10 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="1" t="n">
-        <v>46159</v>
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
@@ -11478,8 +12322,10 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="1" t="n">
-        <v>46153</v>
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
@@ -11504,8 +12350,10 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="1" t="n">
-        <v>46154</v>
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
@@ -11530,8 +12378,10 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="1" t="n">
-        <v>46155</v>
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
@@ -11556,8 +12406,10 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="1" t="n">
-        <v>46156</v>
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
@@ -11582,8 +12434,10 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="1" t="n">
-        <v>46157</v>
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
@@ -11608,8 +12462,10 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="1" t="n">
-        <v>46158</v>
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
@@ -11634,8 +12490,10 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="1" t="n">
-        <v>46153</v>
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
@@ -11660,8 +12518,10 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="1" t="n">
-        <v>46153</v>
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
@@ -11686,8 +12546,10 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="1" t="n">
-        <v>46154</v>
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
@@ -11712,8 +12574,10 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="1" t="n">
-        <v>46155</v>
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
@@ -11738,8 +12602,10 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="1" t="n">
-        <v>46156</v>
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
@@ -11764,8 +12630,10 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="1" t="n">
-        <v>46157</v>
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
@@ -11790,8 +12658,10 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="1" t="n">
-        <v>46158</v>
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
@@ -11816,8 +12686,10 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="1" t="n">
-        <v>46159</v>
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
@@ -11842,8 +12714,10 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="1" t="n">
-        <v>46153</v>
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
@@ -11868,8 +12742,10 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="1" t="n">
-        <v>46154</v>
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
@@ -11894,8 +12770,10 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="1" t="n">
-        <v>46155</v>
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
@@ -11920,8 +12798,10 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="1" t="n">
-        <v>46156</v>
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
@@ -11946,8 +12826,10 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="1" t="n">
-        <v>46157</v>
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
@@ -11972,8 +12854,10 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="1" t="n">
-        <v>46158</v>
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
@@ -11998,8 +12882,10 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="1" t="n">
-        <v>46153</v>
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
@@ -12024,8 +12910,10 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="1" t="n">
-        <v>46153</v>
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
@@ -12050,8 +12938,10 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="1" t="n">
-        <v>46154</v>
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
@@ -12076,8 +12966,10 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="1" t="n">
-        <v>46155</v>
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
@@ -12102,8 +12994,10 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="1" t="n">
-        <v>46156</v>
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
@@ -12128,8 +13022,10 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="1" t="n">
-        <v>46157</v>
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
@@ -12154,8 +13050,10 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="1" t="n">
-        <v>46158</v>
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
@@ -12180,8 +13078,10 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="1" t="n">
-        <v>46159</v>
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
@@ -12206,8 +13106,10 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="1" t="n">
-        <v>46153</v>
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
@@ -12232,8 +13134,10 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="1" t="n">
-        <v>46154</v>
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
@@ -12258,8 +13162,10 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="1" t="n">
-        <v>46155</v>
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
@@ -12284,8 +13190,10 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="1" t="n">
-        <v>46156</v>
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
@@ -12310,8 +13218,10 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="1" t="n">
-        <v>46157</v>
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
@@ -12336,8 +13246,10 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="1" t="n">
-        <v>46158</v>
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
@@ -12362,8 +13274,10 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="1" t="n">
-        <v>46159</v>
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
@@ -12388,8 +13302,10 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="1" t="n">
-        <v>46153</v>
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
@@ -12414,8 +13330,10 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="1" t="n">
-        <v>46153</v>
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
@@ -12440,8 +13358,10 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="1" t="n">
-        <v>46153</v>
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
@@ -12466,8 +13386,10 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="1" t="n">
-        <v>46154</v>
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
@@ -12492,8 +13414,10 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="1" t="n">
-        <v>46154</v>
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
@@ -12518,8 +13442,10 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="1" t="n">
-        <v>46155</v>
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
@@ -12544,8 +13470,10 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="1" t="n">
-        <v>46155</v>
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
@@ -12570,8 +13498,10 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="1" t="n">
-        <v>46156</v>
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
@@ -12596,8 +13526,10 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="1" t="n">
-        <v>46156</v>
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
@@ -12622,8 +13554,10 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="1" t="n">
-        <v>46157</v>
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
@@ -12648,8 +13582,10 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="1" t="n">
-        <v>46157</v>
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
@@ -12674,8 +13610,10 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="1" t="n">
-        <v>46158</v>
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
@@ -12700,8 +13638,10 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="1" t="n">
-        <v>46158</v>
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
@@ -12726,8 +13666,10 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="1" t="n">
-        <v>46159</v>
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
@@ -12752,8 +13694,10 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="1" t="n">
-        <v>46153</v>
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
@@ -12778,8 +13722,10 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="1" t="n">
-        <v>46154</v>
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
@@ -12804,8 +13750,10 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="1" t="n">
-        <v>46155</v>
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
@@ -12830,8 +13778,10 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="1" t="n">
-        <v>46156</v>
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
@@ -12856,8 +13806,10 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="1" t="n">
-        <v>46157</v>
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
@@ -12882,8 +13834,10 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="1" t="n">
-        <v>46158</v>
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
@@ -12908,8 +13862,10 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="1" t="n">
-        <v>46153</v>
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
@@ -12934,8 +13890,10 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="1" t="n">
-        <v>46153</v>
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
@@ -12960,8 +13918,10 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="1" t="n">
-        <v>46154</v>
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
@@ -12986,8 +13946,10 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="1" t="n">
-        <v>46155</v>
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
@@ -13012,8 +13974,10 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="1" t="n">
-        <v>46156</v>
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
@@ -13038,8 +14002,10 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="1" t="n">
-        <v>46157</v>
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
@@ -13064,8 +14030,10 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="1" t="n">
-        <v>46158</v>
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
@@ -13090,8 +14058,10 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="1" t="n">
-        <v>46159</v>
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
@@ -13116,8 +14086,10 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="1" t="n">
-        <v>46153</v>
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
@@ -13142,8 +14114,10 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="1" t="n">
-        <v>46154</v>
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
@@ -13168,8 +14142,10 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" s="1" t="n">
-        <v>46155</v>
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
@@ -13194,8 +14170,10 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" s="1" t="n">
-        <v>46156</v>
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
@@ -13220,8 +14198,10 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" s="1" t="n">
-        <v>46157</v>
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
@@ -13246,8 +14226,10 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" s="1" t="n">
-        <v>46158</v>
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
@@ -13272,8 +14254,10 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="1" t="n">
-        <v>46159</v>
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
@@ -13298,8 +14282,10 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="1" t="n">
-        <v>46153</v>
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
@@ -13324,8 +14310,10 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="1" t="n">
-        <v>46153</v>
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
@@ -13350,8 +14338,10 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" s="1" t="n">
-        <v>46153</v>
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
@@ -13376,8 +14366,10 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" s="1" t="n">
-        <v>46154</v>
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
@@ -13402,8 +14394,10 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="1" t="n">
-        <v>46154</v>
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
@@ -13428,8 +14422,10 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="1" t="n">
-        <v>46155</v>
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
@@ -13454,8 +14450,10 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="1" t="n">
-        <v>46155</v>
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
@@ -13480,8 +14478,10 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" s="1" t="n">
-        <v>46156</v>
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
@@ -13506,8 +14506,10 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" s="1" t="n">
-        <v>46156</v>
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
@@ -13532,8 +14534,10 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="1" t="n">
-        <v>46157</v>
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
@@ -13558,8 +14562,10 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" s="1" t="n">
-        <v>46157</v>
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
@@ -13584,8 +14590,10 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="1" t="n">
-        <v>46158</v>
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
@@ -13610,8 +14618,10 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" s="1" t="n">
-        <v>46159</v>
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
@@ -13636,8 +14646,10 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="1" t="n">
-        <v>46153</v>
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
@@ -13662,8 +14674,10 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" s="1" t="n">
-        <v>46153</v>
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
@@ -13688,8 +14702,10 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="1" t="n">
-        <v>46154</v>
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
@@ -13714,8 +14730,10 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="1" t="n">
-        <v>46154</v>
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
@@ -13740,8 +14758,10 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="1" t="n">
-        <v>46155</v>
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
@@ -13766,8 +14786,10 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" s="1" t="n">
-        <v>46155</v>
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
@@ -13792,8 +14814,10 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" s="1" t="n">
-        <v>46156</v>
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
@@ -13818,8 +14842,10 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" s="1" t="n">
-        <v>46157</v>
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
@@ -13844,8 +14870,10 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" s="1" t="n">
-        <v>46158</v>
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
@@ -13870,8 +14898,10 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="1" t="n">
-        <v>46159</v>
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
@@ -13896,8 +14926,10 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" s="1" t="n">
-        <v>46153</v>
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
@@ -13922,8 +14954,10 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="1" t="n">
-        <v>46153</v>
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
@@ -13948,8 +14982,10 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="1" t="n">
-        <v>46153</v>
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
@@ -13974,8 +15010,10 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" s="1" t="n">
-        <v>46154</v>
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
@@ -14000,8 +15038,10 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="1" t="n">
-        <v>46154</v>
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
@@ -14026,8 +15066,10 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="1" t="n">
-        <v>46155</v>
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
@@ -14052,8 +15094,10 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="1" t="n">
-        <v>46155</v>
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
@@ -14078,8 +15122,10 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" s="1" t="n">
-        <v>46156</v>
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
@@ -14104,8 +15150,10 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" s="1" t="n">
-        <v>46156</v>
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
@@ -14130,8 +15178,10 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" s="1" t="n">
-        <v>46157</v>
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
@@ -14156,8 +15206,10 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="1" t="n">
-        <v>46157</v>
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
@@ -14182,8 +15234,10 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" s="1" t="n">
-        <v>46158</v>
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
@@ -14208,8 +15262,10 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="1" t="n">
-        <v>46159</v>
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
@@ -14234,8 +15290,10 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" s="1" t="n">
-        <v>46153</v>
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
@@ -14260,8 +15318,10 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" s="1" t="n">
-        <v>46153</v>
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
@@ -14286,8 +15346,10 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="1" t="n">
-        <v>46154</v>
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
@@ -14312,8 +15374,10 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="1" t="n">
-        <v>46155</v>
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
@@ -14338,8 +15402,10 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="1" t="n">
-        <v>46156</v>
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
@@ -14364,8 +15430,10 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="1" t="n">
-        <v>46157</v>
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
@@ -14390,8 +15458,10 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" s="1" t="n">
-        <v>46158</v>
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
@@ -14416,8 +15486,10 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="1" t="n">
-        <v>46159</v>
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
@@ -14442,8 +15514,10 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="1" t="n">
-        <v>46153</v>
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
@@ -14468,8 +15542,10 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="1" t="n">
-        <v>46154</v>
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
@@ -14494,8 +15570,10 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" s="1" t="n">
-        <v>46155</v>
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
@@ -14520,8 +15598,10 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="1" t="n">
-        <v>46156</v>
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
@@ -14546,8 +15626,10 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" s="1" t="n">
-        <v>46157</v>
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
@@ -14572,8 +15654,10 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" s="1" t="n">
-        <v>46158</v>
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
@@ -14598,8 +15682,10 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" s="1" t="n">
-        <v>46159</v>
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
@@ -14624,8 +15710,10 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" s="1" t="n">
-        <v>46153</v>
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
@@ -14650,8 +15738,10 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="1" t="n">
-        <v>46154</v>
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
@@ -14676,8 +15766,10 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" s="1" t="n">
-        <v>46155</v>
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
@@ -14702,8 +15794,10 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" s="1" t="n">
-        <v>46156</v>
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
@@ -14728,8 +15822,10 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" s="1" t="n">
-        <v>46157</v>
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
@@ -14754,8 +15850,10 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" s="1" t="n">
-        <v>46158</v>
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
@@ -14780,8 +15878,10 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" s="1" t="n">
-        <v>46159</v>
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
@@ -14806,8 +15906,10 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" s="1" t="n">
-        <v>46153</v>
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
@@ -14832,8 +15934,10 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" s="1" t="n">
-        <v>46153</v>
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
@@ -14858,8 +15962,10 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" s="1" t="n">
-        <v>46153</v>
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
@@ -14884,8 +15990,10 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" s="1" t="n">
-        <v>46154</v>
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
@@ -14910,8 +16018,10 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" s="1" t="n">
-        <v>46154</v>
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
@@ -14936,8 +16046,10 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" s="1" t="n">
-        <v>46155</v>
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
@@ -14962,8 +16074,10 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" s="1" t="n">
-        <v>46155</v>
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
@@ -14988,8 +16102,10 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" s="1" t="n">
-        <v>46156</v>
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
@@ -15014,8 +16130,10 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" s="1" t="n">
-        <v>46156</v>
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
@@ -15040,8 +16158,10 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" s="1" t="n">
-        <v>46157</v>
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
@@ -15066,8 +16186,10 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" s="1" t="n">
-        <v>46157</v>
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
@@ -15092,8 +16214,10 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" s="1" t="n">
-        <v>46158</v>
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
@@ -15118,8 +16242,10 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" s="1" t="n">
-        <v>46158</v>
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
@@ -15144,8 +16270,10 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" s="1" t="n">
-        <v>46159</v>
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
@@ -15170,8 +16298,10 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" s="1" t="n">
-        <v>46159</v>
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
@@ -15196,8 +16326,10 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="1" t="n">
-        <v>46153</v>
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
@@ -15222,8 +16354,10 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" s="1" t="n">
-        <v>46154</v>
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
@@ -15248,8 +16382,10 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" s="1" t="n">
-        <v>46155</v>
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
@@ -15274,8 +16410,10 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" s="1" t="n">
-        <v>46156</v>
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
@@ -15300,8 +16438,10 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" s="1" t="n">
-        <v>46157</v>
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
@@ -15326,8 +16466,10 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" s="1" t="n">
-        <v>46158</v>
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
@@ -15352,8 +16494,10 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" s="1" t="n">
-        <v>46159</v>
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
@@ -15378,8 +16522,10 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" s="1" t="n">
-        <v>46153</v>
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
@@ -15404,8 +16550,10 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" s="1" t="n">
-        <v>46154</v>
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
@@ -15430,8 +16578,10 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" s="1" t="n">
-        <v>46155</v>
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
@@ -15456,8 +16606,10 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" s="1" t="n">
-        <v>46156</v>
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
@@ -15482,8 +16634,10 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" s="1" t="n">
-        <v>46157</v>
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
@@ -15508,8 +16662,10 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" s="1" t="n">
-        <v>46158</v>
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
@@ -15534,8 +16690,10 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" s="1" t="n">
-        <v>46159</v>
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
@@ -15560,8 +16718,10 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" s="1" t="n">
-        <v>46153</v>
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
@@ -15586,8 +16746,10 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" s="1" t="n">
-        <v>46154</v>
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
@@ -15612,8 +16774,10 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" s="1" t="n">
-        <v>46155</v>
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
@@ -15638,8 +16802,10 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" s="1" t="n">
-        <v>46156</v>
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
@@ -15664,8 +16830,10 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" s="1" t="n">
-        <v>46157</v>
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
@@ -15690,8 +16858,10 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" s="1" t="n">
-        <v>46158</v>
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
@@ -15716,8 +16886,10 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" s="1" t="n">
-        <v>46159</v>
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
@@ -15742,8 +16914,10 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" s="1" t="n">
-        <v>46153</v>
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
@@ -15768,8 +16942,10 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" s="1" t="n">
-        <v>46153</v>
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
@@ -15794,8 +16970,10 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" s="1" t="n">
-        <v>46153</v>
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
@@ -15820,8 +16998,10 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" s="1" t="n">
-        <v>46154</v>
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
@@ -15846,8 +17026,10 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" s="1" t="n">
-        <v>46154</v>
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
@@ -15872,8 +17054,10 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" s="1" t="n">
-        <v>46155</v>
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
@@ -15898,8 +17082,10 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" s="1" t="n">
-        <v>46155</v>
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
@@ -15924,8 +17110,10 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" s="1" t="n">
-        <v>46156</v>
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
@@ -15950,8 +17138,10 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" s="1" t="n">
-        <v>46156</v>
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
@@ -15976,8 +17166,10 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" s="1" t="n">
-        <v>46157</v>
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
@@ -16002,8 +17194,10 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" s="1" t="n">
-        <v>46157</v>
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
@@ -16028,8 +17222,10 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" s="1" t="n">
-        <v>46158</v>
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
@@ -16054,8 +17250,10 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" s="1" t="n">
-        <v>46159</v>
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
@@ -16080,8 +17278,10 @@
       </c>
     </row>
     <row r="603">
-      <c r="A603" s="1" t="n">
-        <v>46153</v>
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
@@ -16106,8 +17306,10 @@
       </c>
     </row>
     <row r="604">
-      <c r="A604" s="1" t="n">
-        <v>46154</v>
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
@@ -16132,8 +17334,10 @@
       </c>
     </row>
     <row r="605">
-      <c r="A605" s="1" t="n">
-        <v>46155</v>
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
@@ -16158,8 +17362,10 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" s="1" t="n">
-        <v>46156</v>
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
@@ -16184,8 +17390,10 @@
       </c>
     </row>
     <row r="607">
-      <c r="A607" s="1" t="n">
-        <v>46157</v>
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
@@ -16210,8 +17418,10 @@
       </c>
     </row>
     <row r="608">
-      <c r="A608" s="1" t="n">
-        <v>46158</v>
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
@@ -16236,8 +17446,10 @@
       </c>
     </row>
     <row r="609">
-      <c r="A609" s="1" t="n">
-        <v>46159</v>
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
@@ -16262,8 +17474,10 @@
       </c>
     </row>
     <row r="610">
-      <c r="A610" s="1" t="n">
-        <v>46153</v>
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
@@ -16288,8 +17502,10 @@
       </c>
     </row>
     <row r="611">
-      <c r="A611" s="1" t="n">
-        <v>46153</v>
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
@@ -16314,8 +17530,10 @@
       </c>
     </row>
     <row r="612">
-      <c r="A612" s="1" t="n">
-        <v>46154</v>
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
@@ -16340,8 +17558,10 @@
       </c>
     </row>
     <row r="613">
-      <c r="A613" s="1" t="n">
-        <v>46155</v>
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
@@ -16366,8 +17586,10 @@
       </c>
     </row>
     <row r="614">
-      <c r="A614" s="1" t="n">
-        <v>46156</v>
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
@@ -16392,8 +17614,10 @@
       </c>
     </row>
     <row r="615">
-      <c r="A615" s="1" t="n">
-        <v>46157</v>
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
@@ -16418,8 +17642,10 @@
       </c>
     </row>
     <row r="616">
-      <c r="A616" s="1" t="n">
-        <v>46158</v>
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
@@ -16444,8 +17670,10 @@
       </c>
     </row>
     <row r="617">
-      <c r="A617" s="1" t="n">
-        <v>46159</v>
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
@@ -16470,8 +17698,10 @@
       </c>
     </row>
     <row r="618">
-      <c r="A618" s="1" t="n">
-        <v>46153</v>
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
@@ -16496,8 +17726,10 @@
       </c>
     </row>
     <row r="619">
-      <c r="A619" s="1" t="n">
-        <v>46154</v>
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
@@ -16522,8 +17754,10 @@
       </c>
     </row>
     <row r="620">
-      <c r="A620" s="1" t="n">
-        <v>46155</v>
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
@@ -16548,8 +17782,10 @@
       </c>
     </row>
     <row r="621">
-      <c r="A621" s="1" t="n">
-        <v>46156</v>
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
@@ -16574,8 +17810,10 @@
       </c>
     </row>
     <row r="622">
-      <c r="A622" s="1" t="n">
-        <v>46157</v>
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
@@ -16600,8 +17838,10 @@
       </c>
     </row>
     <row r="623">
-      <c r="A623" s="1" t="n">
-        <v>46158</v>
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
@@ -16626,8 +17866,10 @@
       </c>
     </row>
     <row r="624">
-      <c r="A624" s="1" t="n">
-        <v>46159</v>
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
@@ -16652,8 +17894,10 @@
       </c>
     </row>
     <row r="625">
-      <c r="A625" s="1" t="n">
-        <v>46153</v>
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
@@ -16678,8 +17922,10 @@
       </c>
     </row>
     <row r="626">
-      <c r="A626" s="1" t="n">
-        <v>46153</v>
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
@@ -16704,8 +17950,10 @@
       </c>
     </row>
     <row r="627">
-      <c r="A627" s="1" t="n">
-        <v>46154</v>
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
@@ -16730,8 +17978,10 @@
       </c>
     </row>
     <row r="628">
-      <c r="A628" s="1" t="n">
-        <v>46154</v>
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
@@ -16756,8 +18006,10 @@
       </c>
     </row>
     <row r="629">
-      <c r="A629" s="1" t="n">
-        <v>46155</v>
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
@@ -16782,8 +18034,10 @@
       </c>
     </row>
     <row r="630">
-      <c r="A630" s="1" t="n">
-        <v>46155</v>
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B630" t="inlineStr">
         <is>
@@ -16808,8 +18062,10 @@
       </c>
     </row>
     <row r="631">
-      <c r="A631" s="1" t="n">
-        <v>46156</v>
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
@@ -16834,8 +18090,10 @@
       </c>
     </row>
     <row r="632">
-      <c r="A632" s="1" t="n">
-        <v>46156</v>
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
@@ -16860,8 +18118,10 @@
       </c>
     </row>
     <row r="633">
-      <c r="A633" s="1" t="n">
-        <v>46157</v>
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
@@ -16886,8 +18146,10 @@
       </c>
     </row>
     <row r="634">
-      <c r="A634" s="1" t="n">
-        <v>46157</v>
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
@@ -16912,8 +18174,10 @@
       </c>
     </row>
     <row r="635">
-      <c r="A635" s="1" t="n">
-        <v>46158</v>
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
@@ -16938,8 +18202,10 @@
       </c>
     </row>
     <row r="636">
-      <c r="A636" s="1" t="n">
-        <v>46159</v>
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
@@ -16964,8 +18230,10 @@
       </c>
     </row>
     <row r="637">
-      <c r="A637" s="1" t="n">
-        <v>46153</v>
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
@@ -16990,8 +18258,10 @@
       </c>
     </row>
     <row r="638">
-      <c r="A638" s="1" t="n">
-        <v>46153</v>
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
@@ -17016,8 +18286,10 @@
       </c>
     </row>
     <row r="639">
-      <c r="A639" s="1" t="n">
-        <v>46153</v>
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
@@ -17042,8 +18314,10 @@
       </c>
     </row>
     <row r="640">
-      <c r="A640" s="1" t="n">
-        <v>46154</v>
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
@@ -17068,8 +18342,10 @@
       </c>
     </row>
     <row r="641">
-      <c r="A641" s="1" t="n">
-        <v>46154</v>
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
@@ -17094,8 +18370,10 @@
       </c>
     </row>
     <row r="642">
-      <c r="A642" s="1" t="n">
-        <v>46155</v>
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
@@ -17120,8 +18398,10 @@
       </c>
     </row>
     <row r="643">
-      <c r="A643" s="1" t="n">
-        <v>46155</v>
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
@@ -17146,8 +18426,10 @@
       </c>
     </row>
     <row r="644">
-      <c r="A644" s="1" t="n">
-        <v>46156</v>
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
@@ -17172,8 +18454,10 @@
       </c>
     </row>
     <row r="645">
-      <c r="A645" s="1" t="n">
-        <v>46156</v>
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
@@ -17198,8 +18482,10 @@
       </c>
     </row>
     <row r="646">
-      <c r="A646" s="1" t="n">
-        <v>46157</v>
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
@@ -17224,8 +18510,10 @@
       </c>
     </row>
     <row r="647">
-      <c r="A647" s="1" t="n">
-        <v>46157</v>
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
@@ -17250,8 +18538,10 @@
       </c>
     </row>
     <row r="648">
-      <c r="A648" s="1" t="n">
-        <v>46158</v>
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
@@ -17276,8 +18566,10 @@
       </c>
     </row>
     <row r="649">
-      <c r="A649" s="1" t="n">
-        <v>46158</v>
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
@@ -17302,8 +18594,10 @@
       </c>
     </row>
     <row r="650">
-      <c r="A650" s="1" t="n">
-        <v>46159</v>
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
@@ -17328,8 +18622,10 @@
       </c>
     </row>
     <row r="651">
-      <c r="A651" s="1" t="n">
-        <v>46159</v>
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
@@ -17354,8 +18650,10 @@
       </c>
     </row>
     <row r="652">
-      <c r="A652" s="1" t="n">
-        <v>46153</v>
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
@@ -17380,8 +18678,10 @@
       </c>
     </row>
     <row r="653">
-      <c r="A653" s="1" t="n">
-        <v>46154</v>
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
@@ -17406,8 +18706,10 @@
       </c>
     </row>
     <row r="654">
-      <c r="A654" s="1" t="n">
-        <v>46155</v>
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
@@ -17432,8 +18734,10 @@
       </c>
     </row>
     <row r="655">
-      <c r="A655" s="1" t="n">
-        <v>46156</v>
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
@@ -17458,8 +18762,10 @@
       </c>
     </row>
     <row r="656">
-      <c r="A656" s="1" t="n">
-        <v>46157</v>
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
@@ -17484,8 +18790,10 @@
       </c>
     </row>
     <row r="657">
-      <c r="A657" s="1" t="n">
-        <v>46158</v>
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
@@ -17510,8 +18818,10 @@
       </c>
     </row>
     <row r="658">
-      <c r="A658" s="1" t="n">
-        <v>46159</v>
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
@@ -17536,8 +18846,10 @@
       </c>
     </row>
     <row r="659">
-      <c r="A659" s="1" t="n">
-        <v>46153</v>
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
@@ -17562,8 +18874,10 @@
       </c>
     </row>
     <row r="660">
-      <c r="A660" s="1" t="n">
-        <v>46154</v>
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
@@ -17588,8 +18902,10 @@
       </c>
     </row>
     <row r="661">
-      <c r="A661" s="1" t="n">
-        <v>46155</v>
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
@@ -17614,8 +18930,10 @@
       </c>
     </row>
     <row r="662">
-      <c r="A662" s="1" t="n">
-        <v>46156</v>
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
@@ -17640,8 +18958,10 @@
       </c>
     </row>
     <row r="663">
-      <c r="A663" s="1" t="n">
-        <v>46157</v>
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
@@ -17666,8 +18986,10 @@
       </c>
     </row>
     <row r="664">
-      <c r="A664" s="1" t="n">
-        <v>46158</v>
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
@@ -17692,8 +19014,10 @@
       </c>
     </row>
     <row r="665">
-      <c r="A665" s="1" t="n">
-        <v>46159</v>
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
@@ -17718,8 +19042,10 @@
       </c>
     </row>
     <row r="666">
-      <c r="A666" s="1" t="n">
-        <v>46153</v>
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
@@ -17744,8 +19070,10 @@
       </c>
     </row>
     <row r="667">
-      <c r="A667" s="1" t="n">
-        <v>46154</v>
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
@@ -17770,8 +19098,10 @@
       </c>
     </row>
     <row r="668">
-      <c r="A668" s="1" t="n">
-        <v>46155</v>
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B668" t="inlineStr">
         <is>
@@ -17796,8 +19126,10 @@
       </c>
     </row>
     <row r="669">
-      <c r="A669" s="1" t="n">
-        <v>46156</v>
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
@@ -17822,8 +19154,10 @@
       </c>
     </row>
     <row r="670">
-      <c r="A670" s="1" t="n">
-        <v>46157</v>
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
@@ -17848,8 +19182,10 @@
       </c>
     </row>
     <row r="671">
-      <c r="A671" s="1" t="n">
-        <v>46158</v>
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
@@ -17874,8 +19210,10 @@
       </c>
     </row>
     <row r="672">
-      <c r="A672" s="1" t="n">
-        <v>46153</v>
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
@@ -17900,8 +19238,10 @@
       </c>
     </row>
     <row r="673">
-      <c r="A673" s="1" t="n">
-        <v>46154</v>
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
@@ -17926,8 +19266,10 @@
       </c>
     </row>
     <row r="674">
-      <c r="A674" s="1" t="n">
-        <v>46155</v>
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
@@ -17952,8 +19294,10 @@
       </c>
     </row>
     <row r="675">
-      <c r="A675" s="1" t="n">
-        <v>46156</v>
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
@@ -17978,8 +19322,10 @@
       </c>
     </row>
     <row r="676">
-      <c r="A676" s="1" t="n">
-        <v>46157</v>
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
@@ -18004,8 +19350,10 @@
       </c>
     </row>
     <row r="677">
-      <c r="A677" s="1" t="n">
-        <v>46158</v>
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
@@ -18030,8 +19378,10 @@
       </c>
     </row>
     <row r="678">
-      <c r="A678" s="1" t="n">
-        <v>46153</v>
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
@@ -18056,8 +19406,10 @@
       </c>
     </row>
     <row r="679">
-      <c r="A679" s="1" t="n">
-        <v>46154</v>
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
@@ -18082,8 +19434,10 @@
       </c>
     </row>
     <row r="680">
-      <c r="A680" s="1" t="n">
-        <v>46155</v>
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
@@ -18108,8 +19462,10 @@
       </c>
     </row>
     <row r="681">
-      <c r="A681" s="1" t="n">
-        <v>46156</v>
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
@@ -18134,8 +19490,10 @@
       </c>
     </row>
     <row r="682">
-      <c r="A682" s="1" t="n">
-        <v>46157</v>
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
@@ -18160,8 +19518,10 @@
       </c>
     </row>
     <row r="683">
-      <c r="A683" s="1" t="n">
-        <v>46158</v>
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
@@ -18196,7 +19556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18219,7 +19579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>802,743.79</t>
+          <t>802,743.90</t>
         </is>
       </c>
     </row>
@@ -18231,7 +19591,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9,284,442.92</t>
+          <t>9,284,442.94</t>
         </is>
       </c>
     </row>
@@ -18243,7 +19603,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10,087,186.71</t>
+          <t>10,087,186.84</t>
         </is>
       </c>
     </row>
@@ -18262,60 +19622,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tahmin Modeli</t>
+          <t>Mesafe Hesabi</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P(sevkiyat) x E[desi|sevkiyat] iki-parcali model</t>
+          <t>Haversine kus ucusu (FAQ #6)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tahmin WAPE</t>
+          <t>Not</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>~%42 (backtest 27 Nis - 10 May)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Optimizasyon Yontemi</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>OR-Tools CP-SAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Mesafe Hesabi</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Haversine kus ucusu (FAQ #6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Not</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Kiralik_Araclar listesindeki filo, 7 gunun hepsinde ayni sekilde calistigi varsayilmistir.</t>
+          <t>Kiralik_Araclar 7 gun boyunca sabit calisir</t>
         </is>
       </c>
     </row>
